--- a/reports/pdf_rolling5_20261023.xlsx
+++ b/reports/pdf_rolling5_20261023.xlsx
@@ -569,7 +569,7 @@
     <row r="3" ht="19" customHeight="1">
       <c r="A3" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,594억   ·   현금 27억(0.6%)      오늘 2026-10-23  vs  5일전 2026-10-16      매수 17종목  /  매도 13종목</t>
+          <t>■ KoAct 코스닥액티브  (삼성액티브)      순자산 ≈ 4,380억      오늘 2026-10-23  vs  5일전 2026-10-16      매수 17종목  /  매도 13종목</t>
         </is>
       </c>
       <c r="B3" s="4" t="n"/>
@@ -665,7 +665,7 @@
         <v>426</v>
       </c>
       <c r="C6" s="11" t="n">
-        <v>4259932439</v>
+        <v>4259932097</v>
       </c>
       <c r="D6" s="12" t="inlineStr">
         <is>
@@ -686,7 +686,7 @@
         <v>-176</v>
       </c>
       <c r="I6" s="15" t="n">
-        <v>-1588181983</v>
+        <v>-1588181856</v>
       </c>
       <c r="J6" s="16" t="inlineStr">
         <is>
@@ -709,7 +709,7 @@
         <v>142</v>
       </c>
       <c r="C7" s="11" t="n">
-        <v>3443869684</v>
+        <v>3443869407</v>
       </c>
       <c r="D7" s="12" t="inlineStr">
         <is>
@@ -730,7 +730,7 @@
         <v>-156</v>
       </c>
       <c r="I7" s="15" t="n">
-        <v>-2004350682</v>
+        <v>-2004350521</v>
       </c>
       <c r="J7" s="16" t="inlineStr">
         <is>
@@ -753,7 +753,7 @@
         <v>84</v>
       </c>
       <c r="C8" s="11" t="n">
-        <v>3576636503</v>
+        <v>3576636215</v>
       </c>
       <c r="D8" s="12" t="inlineStr">
         <is>
@@ -774,7 +774,7 @@
         <v>-50</v>
       </c>
       <c r="I8" s="15" t="n">
-        <v>-1319700186</v>
+        <v>-1319700080</v>
       </c>
       <c r="J8" s="16" t="inlineStr">
         <is>
@@ -797,7 +797,7 @@
         <v>78</v>
       </c>
       <c r="C9" s="11" t="n">
-        <v>4661280655</v>
+        <v>4661280281</v>
       </c>
       <c r="D9" s="12" t="inlineStr">
         <is>
@@ -818,7 +818,7 @@
         <v>-34</v>
       </c>
       <c r="I9" s="15" t="n">
-        <v>-2174069106</v>
+        <v>-2174068931</v>
       </c>
       <c r="J9" s="16" t="inlineStr">
         <is>
@@ -841,7 +841,7 @@
         <v>63</v>
       </c>
       <c r="C10" s="11" t="n">
-        <v>874079763</v>
+        <v>874079693</v>
       </c>
       <c r="D10" s="12" t="inlineStr">
         <is>
@@ -862,7 +862,7 @@
         <v>-31</v>
       </c>
       <c r="I10" s="15" t="n">
-        <v>-1296792182</v>
+        <v>-1296792078</v>
       </c>
       <c r="J10" s="16" t="inlineStr">
         <is>
@@ -885,7 +885,7 @@
         <v>60</v>
       </c>
       <c r="C11" s="11" t="n">
-        <v>2659320374</v>
+        <v>2659320160</v>
       </c>
       <c r="D11" s="12" t="inlineStr">
         <is>
@@ -906,7 +906,7 @@
         <v>-26</v>
       </c>
       <c r="I11" s="15" t="n">
-        <v>-397244696</v>
+        <v>-397244664</v>
       </c>
       <c r="J11" s="16" t="inlineStr">
         <is>
@@ -929,7 +929,7 @@
         <v>47</v>
       </c>
       <c r="C12" s="11" t="n">
-        <v>1387975995</v>
+        <v>1387975884</v>
       </c>
       <c r="D12" s="12" t="inlineStr">
         <is>
@@ -950,7 +950,7 @@
         <v>-25</v>
       </c>
       <c r="I12" s="15" t="n">
-        <v>-1142910161</v>
+        <v>-1142910069</v>
       </c>
       <c r="J12" s="16" t="inlineStr">
         <is>
@@ -973,7 +973,7 @@
         <v>44</v>
       </c>
       <c r="C13" s="11" t="n">
-        <v>885244924</v>
+        <v>885244853</v>
       </c>
       <c r="D13" s="12" t="inlineStr">
         <is>
@@ -994,7 +994,7 @@
         <v>-11</v>
       </c>
       <c r="I13" s="15" t="n">
-        <v>-2788302392</v>
+        <v>-2788302168</v>
       </c>
       <c r="J13" s="16" t="inlineStr">
         <is>
@@ -1017,7 +1017,7 @@
         <v>32</v>
       </c>
       <c r="C14" s="11" t="n">
-        <v>1321094586</v>
+        <v>1321094480</v>
       </c>
       <c r="D14" s="12" t="inlineStr">
         <is>
@@ -1038,7 +1038,7 @@
         <v>-8</v>
       </c>
       <c r="I14" s="15" t="n">
-        <v>-1226275372</v>
+        <v>-1226275274</v>
       </c>
       <c r="J14" s="16" t="inlineStr">
         <is>
@@ -1061,7 +1061,7 @@
         <v>31</v>
       </c>
       <c r="C15" s="11" t="n">
-        <v>2627547969</v>
+        <v>2627547758</v>
       </c>
       <c r="D15" s="12" t="inlineStr">
         <is>
@@ -1082,7 +1082,7 @@
         <v>-7</v>
       </c>
       <c r="I15" s="15" t="n">
-        <v>-758553707</v>
+        <v>-758553646</v>
       </c>
       <c r="J15" s="16" t="inlineStr">
         <is>
@@ -1105,7 +1105,7 @@
         <v>29</v>
       </c>
       <c r="C16" s="11" t="n">
-        <v>430371660</v>
+        <v>430371626</v>
       </c>
       <c r="D16" s="12" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>-6</v>
       </c>
       <c r="I16" s="15" t="n">
-        <v>-122508017</v>
+        <v>-122508007</v>
       </c>
       <c r="J16" s="16" t="inlineStr">
         <is>
@@ -1149,7 +1149,7 @@
         <v>25</v>
       </c>
       <c r="C17" s="11" t="n">
-        <v>1307250184</v>
+        <v>1307250079</v>
       </c>
       <c r="D17" s="12" t="inlineStr">
         <is>
@@ -1170,7 +1170,7 @@
         <v>-5</v>
       </c>
       <c r="I17" s="15" t="n">
-        <v>-1018410143</v>
+        <v>-1018410061</v>
       </c>
       <c r="J17" s="16" t="inlineStr">
         <is>
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>413539258</v>
+        <v>586245635</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.47%→1.46%</t>
+          <t>0.46%→0.52%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>173→185</t>
+          <t>34→46</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1214,7 +1214,7 @@
         <v>-4</v>
       </c>
       <c r="I18" s="15" t="n">
-        <v>-671304094</v>
+        <v>-671304040</v>
       </c>
       <c r="J18" s="16" t="inlineStr">
         <is>
@@ -1230,23 +1230,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>2958120416</v>
+        <v>413539225</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>1.50%→2.10%</t>
+          <t>1.47%→1.46%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>25→37</t>
+          <t>173→185</t>
         </is>
       </c>
       <c r="G19" s="17" t="n"/>
@@ -1258,23 +1258,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>586245682</v>
+        <v>2958120178</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>0.46%→0.52%</t>
+          <t>1.50%→2.10%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>34→46</t>
+          <t>25→37</t>
         </is>
       </c>
       <c r="G20" s="17" t="n"/>
@@ -1293,7 +1293,7 @@
         <v>9</v>
       </c>
       <c r="C21" s="11" t="n">
-        <v>2070684291</v>
+        <v>2070684125</v>
       </c>
       <c r="D21" s="12" t="inlineStr">
         <is>
@@ -1321,7 +1321,7 @@
         <v>8</v>
       </c>
       <c r="C22" s="11" t="n">
-        <v>841420918</v>
+        <v>841420851</v>
       </c>
       <c r="D22" s="12" t="inlineStr">
         <is>
@@ -1342,7 +1342,7 @@
     <row r="24" ht="19" customHeight="1">
       <c r="A24" s="3" t="inlineStr">
         <is>
-          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,216억   ·   현금 60억(1.9%)      오늘 2026-10-23  vs  5일전 2026-10-16      매수 5종목  /  매도 2종목</t>
+          <t>■ KoAct 바이오헬스케어액티브  (삼성액티브)      순자산 ≈ 3,140억      오늘 2026-10-23  vs  5일전 2026-10-16      매수 5종목  /  매도 2종목</t>
         </is>
       </c>
       <c r="B24" s="4" t="n"/>
@@ -1438,7 +1438,7 @@
         <v>39</v>
       </c>
       <c r="C27" s="11" t="n">
-        <v>840859500</v>
+        <v>844002837</v>
       </c>
       <c r="D27" s="12" t="inlineStr">
         <is>
@@ -1459,7 +1459,7 @@
         <v>-90</v>
       </c>
       <c r="I27" s="15" t="n">
-        <v>-630765000</v>
+        <v>-633122953</v>
       </c>
       <c r="J27" s="16" t="inlineStr">
         <is>
@@ -1482,7 +1482,7 @@
         <v>26</v>
       </c>
       <c r="C28" s="11" t="n">
-        <v>618995000</v>
+        <v>621308954</v>
       </c>
       <c r="D28" s="12" t="inlineStr">
         <is>
@@ -1503,7 +1503,7 @@
         <v>-17</v>
       </c>
       <c r="I28" s="15" t="n">
-        <v>-1767158500</v>
+        <v>-1773764568</v>
       </c>
       <c r="J28" s="16" t="inlineStr">
         <is>
@@ -1526,7 +1526,7 @@
         <v>12</v>
       </c>
       <c r="C29" s="11" t="n">
-        <v>677952000</v>
+        <v>680486349</v>
       </c>
       <c r="D29" s="12" t="inlineStr">
         <is>
@@ -1554,7 +1554,7 @@
         <v>5</v>
       </c>
       <c r="C30" s="11" t="n">
-        <v>617925000</v>
+        <v>620234954</v>
       </c>
       <c r="D30" s="12" t="inlineStr">
         <is>
@@ -1582,7 +1582,7 @@
         <v>4</v>
       </c>
       <c r="C31" s="11" t="n">
-        <v>283764000</v>
+        <v>284824779</v>
       </c>
       <c r="D31" s="12" t="inlineStr">
         <is>
@@ -1603,7 +1603,7 @@
     <row r="33" ht="19" customHeight="1">
       <c r="A33" s="3" t="inlineStr">
         <is>
-          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,348억   ·   현금 37억(1.7%)      오늘 2026-10-23  vs  5일전 2026-10-16      매수 14종목  /  매도 23종목</t>
+          <t>■ TIME 코스닥액티브  (타임폴리오)      순자산 ≈ 2,218억      오늘 2026-10-23  vs  5일전 2026-10-16      매수 14종목  /  매도 23종목</t>
         </is>
       </c>
       <c r="B33" s="4" t="n"/>
@@ -1699,7 +1699,7 @@
         <v>800</v>
       </c>
       <c r="C36" s="11" t="n">
-        <v>5346168809</v>
+        <v>5338077088</v>
       </c>
       <c r="D36" s="12" t="inlineStr">
         <is>
@@ -1720,7 +1720,7 @@
         <v>-230</v>
       </c>
       <c r="I36" s="15" t="n">
-        <v>-7358253113</v>
+        <v>-7347115992</v>
       </c>
       <c r="J36" s="16" t="inlineStr">
         <is>
@@ -1743,7 +1743,7 @@
         <v>299</v>
       </c>
       <c r="C37" s="11" t="n">
-        <v>4545697688</v>
+        <v>4538817524</v>
       </c>
       <c r="D37" s="12" t="inlineStr">
         <is>
@@ -1764,7 +1764,7 @@
         <v>-202</v>
       </c>
       <c r="I37" s="15" t="n">
-        <v>-1191016420</v>
+        <v>-1189213751</v>
       </c>
       <c r="J37" s="16" t="inlineStr">
         <is>
@@ -1787,7 +1787,7 @@
         <v>250</v>
       </c>
       <c r="C38" s="11" t="n">
-        <v>7006601060</v>
+        <v>6995996184</v>
       </c>
       <c r="D38" s="12" t="inlineStr">
         <is>
@@ -1808,7 +1808,7 @@
         <v>-112</v>
       </c>
       <c r="I38" s="15" t="n">
-        <v>-1181550899</v>
+        <v>-1179762556</v>
       </c>
       <c r="J38" s="16" t="inlineStr">
         <is>
@@ -1831,7 +1831,7 @@
         <v>230</v>
       </c>
       <c r="C39" s="11" t="n">
-        <v>10763725628</v>
+        <v>10747434138</v>
       </c>
       <c r="D39" s="12" t="inlineStr">
         <is>
@@ -1852,7 +1852,7 @@
         <v>-108</v>
       </c>
       <c r="I39" s="15" t="n">
-        <v>-2634217599</v>
+        <v>-2630230565</v>
       </c>
       <c r="J39" s="16" t="inlineStr">
         <is>
@@ -1875,7 +1875,7 @@
         <v>200</v>
       </c>
       <c r="C40" s="11" t="n">
-        <v>12373921872</v>
+        <v>12355193261</v>
       </c>
       <c r="D40" s="12" t="inlineStr">
         <is>
@@ -1896,7 +1896,7 @@
         <v>-97</v>
       </c>
       <c r="I40" s="15" t="n">
-        <v>-1590101841</v>
+        <v>-1587695134</v>
       </c>
       <c r="J40" s="16" t="inlineStr">
         <is>
@@ -1919,7 +1919,7 @@
         <v>151</v>
       </c>
       <c r="C41" s="11" t="n">
-        <v>1331478941</v>
+        <v>1329463675</v>
       </c>
       <c r="D41" s="12" t="inlineStr">
         <is>
@@ -1940,7 +1940,7 @@
         <v>-85</v>
       </c>
       <c r="I41" s="15" t="n">
-        <v>-6112928925</v>
+        <v>-6103676671</v>
       </c>
       <c r="J41" s="16" t="inlineStr">
         <is>
@@ -1963,7 +1963,7 @@
         <v>150</v>
       </c>
       <c r="C42" s="11" t="n">
-        <v>3782573072</v>
+        <v>3776847940</v>
       </c>
       <c r="D42" s="12" t="inlineStr">
         <is>
@@ -1984,7 +1984,7 @@
         <v>-65</v>
       </c>
       <c r="I42" s="15" t="n">
-        <v>-1804530273</v>
+        <v>-1801799017</v>
       </c>
       <c r="J42" s="16" t="inlineStr">
         <is>
@@ -2007,7 +2007,7 @@
         <v>99</v>
       </c>
       <c r="C43" s="11" t="n">
-        <v>2277277545</v>
+        <v>2273830760</v>
       </c>
       <c r="D43" s="12" t="inlineStr">
         <is>
@@ -2028,7 +2028,7 @@
         <v>-50</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-766760116</v>
+        <v>-765599582</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
@@ -2051,7 +2051,7 @@
         <v>85</v>
       </c>
       <c r="C44" s="11" t="n">
-        <v>1261353441</v>
+        <v>1259444313</v>
       </c>
       <c r="D44" s="12" t="inlineStr">
         <is>
@@ -2065,23 +2065,23 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에이치브이엠  (편출)</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-2657220402</v>
+        <v>-1841398996</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>4.06%→3.16%</t>
+          <t>0.83%→0.00%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
         <is>
-          <t>180→130</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -2095,7 +2095,7 @@
         <v>60</v>
       </c>
       <c r="C45" s="11" t="n">
-        <v>4739370717</v>
+        <v>4732197419</v>
       </c>
       <c r="D45" s="12" t="inlineStr">
         <is>
@@ -2109,23 +2109,23 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠  (편출)</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-1844190279</v>
+        <v>-2653198553</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>0.83%→0.00%</t>
+          <t>4.06%→3.16%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>180→130</t>
         </is>
       </c>
     </row>
@@ -2139,7 +2139,7 @@
         <v>50</v>
       </c>
       <c r="C46" s="11" t="n">
-        <v>3592535544</v>
+        <v>3587098043</v>
       </c>
       <c r="D46" s="12" t="inlineStr">
         <is>
@@ -2160,7 +2160,7 @@
         <v>-44</v>
       </c>
       <c r="I46" s="15" t="n">
-        <v>-2245285140</v>
+        <v>-2241886777</v>
       </c>
       <c r="J46" s="16" t="inlineStr">
         <is>
@@ -2183,7 +2183,7 @@
         <v>16</v>
       </c>
       <c r="C47" s="11" t="n">
-        <v>1106249767</v>
+        <v>1104575398</v>
       </c>
       <c r="D47" s="12" t="inlineStr">
         <is>
@@ -2204,7 +2204,7 @@
         <v>-41</v>
       </c>
       <c r="I47" s="15" t="n">
-        <v>-6897205543</v>
+        <v>-6886766244</v>
       </c>
       <c r="J47" s="16" t="inlineStr">
         <is>
@@ -2227,7 +2227,7 @@
         <v>15</v>
       </c>
       <c r="C48" s="11" t="n">
-        <v>1670677753</v>
+        <v>1668149090</v>
       </c>
       <c r="D48" s="12" t="inlineStr">
         <is>
@@ -2248,7 +2248,7 @@
         <v>-39</v>
       </c>
       <c r="I48" s="15" t="n">
-        <v>-2487673876</v>
+        <v>-2483908645</v>
       </c>
       <c r="J48" s="16" t="inlineStr">
         <is>
@@ -2271,7 +2271,7 @@
         <v>6</v>
       </c>
       <c r="C49" s="11" t="n">
-        <v>464815270</v>
+        <v>464111747</v>
       </c>
       <c r="D49" s="12" t="inlineStr">
         <is>
@@ -2292,7 +2292,7 @@
         <v>-30</v>
       </c>
       <c r="I49" s="15" t="n">
-        <v>-3702261560</v>
+        <v>-3696657984</v>
       </c>
       <c r="J49" s="16" t="inlineStr">
         <is>
@@ -2320,7 +2320,7 @@
         <v>-25</v>
       </c>
       <c r="I50" s="15" t="n">
-        <v>-670088851</v>
+        <v>-669074635</v>
       </c>
       <c r="J50" s="16" t="inlineStr">
         <is>
@@ -2348,7 +2348,7 @@
         <v>-24</v>
       </c>
       <c r="I51" s="15" t="n">
-        <v>-3680448557</v>
+        <v>-3674877996</v>
       </c>
       <c r="J51" s="16" t="inlineStr">
         <is>
@@ -2376,7 +2376,7 @@
         <v>-19</v>
       </c>
       <c r="I52" s="15" t="n">
-        <v>-3196265984</v>
+        <v>-3191428259</v>
       </c>
       <c r="J52" s="16" t="inlineStr">
         <is>
@@ -2397,23 +2397,23 @@
       <c r="E53" s="17" t="n"/>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-4336160656</v>
+        <v>-1092959404</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>5.76%→3.72%</t>
+          <t>3.18%→2.29%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>46→30</t>
+          <t>89→73</t>
         </is>
       </c>
     </row>
@@ -2425,23 +2425,23 @@
       <c r="E54" s="17" t="n"/>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-1094616166</v>
+        <v>-4329597638</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>3.18%→2.29%</t>
+          <t>5.76%→3.72%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>89→73</t>
+          <t>46→30</t>
         </is>
       </c>
     </row>
@@ -2460,7 +2460,7 @@
         <v>-15</v>
       </c>
       <c r="I55" s="15" t="n">
-        <v>-1525918731</v>
+        <v>-1523609169</v>
       </c>
       <c r="J55" s="16" t="inlineStr">
         <is>
@@ -2481,23 +2481,23 @@
       <c r="E56" s="17" t="n"/>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>보로노이  (편출)</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-599130491</v>
+        <v>-1927198949</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.00%</t>
+          <t>2.76%→2.10%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>8→0</t>
+          <t>27→19</t>
         </is>
       </c>
     </row>
@@ -2509,23 +2509,23 @@
       <c r="E57" s="17" t="n"/>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>보로노이  (편출)</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-1930120292</v>
+        <v>-598223674</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>2.76%→2.10%</t>
+          <t>0.27%→0.00%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>27→19</t>
+          <t>8→0</t>
         </is>
       </c>
     </row>
@@ -2544,7 +2544,7 @@
         <v>-7</v>
       </c>
       <c r="I58" s="15" t="n">
-        <v>-1196079681</v>
+        <v>-1194269349</v>
       </c>
       <c r="J58" s="16" t="inlineStr">
         <is>
@@ -2560,7 +2560,7 @@
     <row r="60" ht="19" customHeight="1">
       <c r="A60" s="3" t="inlineStr">
         <is>
-          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,142억   ·   현금 1억(0.1%)      오늘 2026-10-23  vs  5일전 2026-10-16      매수 5종목  /  매도 3종목</t>
+          <t>■ TIME K바이오액티브  (타임폴리오)      순자산 ≈ 2,131억      오늘 2026-10-23  vs  5일전 2026-10-16      매수 5종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B60" s="4" t="n"/>
@@ -2656,7 +2656,7 @@
         <v>209</v>
       </c>
       <c r="C63" s="11" t="n">
-        <v>2066884600</v>
+        <v>2119343810</v>
       </c>
       <c r="D63" s="12" t="inlineStr">
         <is>
@@ -2677,7 +2677,7 @@
         <v>-389</v>
       </c>
       <c r="I63" s="15" t="n">
-        <v>-3172606200</v>
+        <v>-3253129522</v>
       </c>
       <c r="J63" s="16" t="inlineStr">
         <is>
@@ -2700,7 +2700,7 @@
         <v>104</v>
       </c>
       <c r="C64" s="11" t="n">
-        <v>4327065600</v>
+        <v>4436890039</v>
       </c>
       <c r="D64" s="12" t="inlineStr">
         <is>
@@ -2721,7 +2721,7 @@
         <v>-311</v>
       </c>
       <c r="I64" s="15" t="n">
-        <v>-4938120200</v>
+        <v>-5063453701</v>
       </c>
       <c r="J64" s="16" t="inlineStr">
         <is>
@@ -2744,7 +2744,7 @@
         <v>14</v>
       </c>
       <c r="C65" s="11" t="n">
-        <v>2043678000</v>
+        <v>2095548207</v>
       </c>
       <c r="D65" s="12" t="inlineStr">
         <is>
@@ -2765,7 +2765,7 @@
         <v>-62</v>
       </c>
       <c r="I65" s="15" t="n">
-        <v>-1003990800</v>
+        <v>-1029472902</v>
       </c>
       <c r="J65" s="16" t="inlineStr">
         <is>
@@ -2788,7 +2788,7 @@
         <v>9</v>
       </c>
       <c r="C66" s="11" t="n">
-        <v>4826106000</v>
+        <v>4948596490</v>
       </c>
       <c r="D66" s="12" t="inlineStr">
         <is>
@@ -2816,7 +2816,7 @@
         <v>7</v>
       </c>
       <c r="C67" s="11" t="n">
-        <v>535879400</v>
+        <v>549480454</v>
       </c>
       <c r="D67" s="12" t="inlineStr">
         <is>
@@ -2837,7 +2837,7 @@
     <row r="69" ht="19" customHeight="1">
       <c r="A69" s="3" t="inlineStr">
         <is>
-          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 258억   ·   현금 2억(0.9%)      오늘 2026-10-23  vs  5일전 2026-10-16      매수 9종목  /  매도 7종목</t>
+          <t>■ PLUS 코스닥150액티브  (한화)      순자산 ≈ 248억      오늘 2026-10-23  vs  5일전 2026-10-16      매수 9종목  /  매도 7종목</t>
         </is>
       </c>
       <c r="B69" s="4" t="n"/>
@@ -2933,11 +2933,11 @@
         <v>199</v>
       </c>
       <c r="C72" s="11" t="n">
-        <v>115133440</v>
+        <v>103798368</v>
       </c>
       <c r="D72" s="12" t="inlineStr">
         <is>
-          <t>6.94%→7.36%</t>
+          <t>6.52%→6.92%</t>
         </is>
       </c>
       <c r="E72" s="13" t="inlineStr">
@@ -2954,11 +2954,11 @@
         <v>-26</v>
       </c>
       <c r="I72" s="15" t="n">
-        <v>-83699200</v>
+        <v>-82284774</v>
       </c>
       <c r="J72" s="16" t="inlineStr">
         <is>
-          <t>3.26%→2.92%</t>
+          <t>3.34%→2.99%</t>
         </is>
       </c>
       <c r="K72" s="13" t="inlineStr">
@@ -2977,11 +2977,11 @@
         <v>61</v>
       </c>
       <c r="C73" s="11" t="n">
-        <v>99942400</v>
+        <v>93695971</v>
       </c>
       <c r="D73" s="12" t="inlineStr">
         <is>
-          <t>0.00%→0.39%</t>
+          <t>0.00%→0.38%</t>
         </is>
       </c>
       <c r="E73" s="13" t="inlineStr">
@@ -2998,11 +2998,11 @@
         <v>-24</v>
       </c>
       <c r="I73" s="15" t="n">
-        <v>-87398400</v>
+        <v>-85862373</v>
       </c>
       <c r="J73" s="16" t="inlineStr">
         <is>
-          <t>4.56%→4.20%</t>
+          <t>4.67%→4.30%</t>
         </is>
       </c>
       <c r="K73" s="13" t="inlineStr">
@@ -3021,11 +3021,11 @@
         <v>34</v>
       </c>
       <c r="C74" s="11" t="n">
-        <v>30333440</v>
+        <v>30311671</v>
       </c>
       <c r="D74" s="12" t="inlineStr">
         <is>
-          <t>0.31%→0.43%</t>
+          <t>0.32%→0.45%</t>
         </is>
       </c>
       <c r="E74" s="13" t="inlineStr">
@@ -3042,11 +3042,11 @@
         <v>-22</v>
       </c>
       <c r="I74" s="15" t="n">
-        <v>-45478400</v>
+        <v>-42943987</v>
       </c>
       <c r="J74" s="16" t="inlineStr">
         <is>
-          <t>0.28%→0.10%</t>
+          <t>0.27%→0.10%</t>
         </is>
       </c>
       <c r="K74" s="13" t="inlineStr">
@@ -3065,11 +3065,11 @@
         <v>24</v>
       </c>
       <c r="C75" s="11" t="n">
-        <v>49612800</v>
+        <v>47923185</v>
       </c>
       <c r="D75" s="12" t="inlineStr">
         <is>
-          <t>1.28%→1.47%</t>
+          <t>1.29%→1.48%</t>
         </is>
       </c>
       <c r="E75" s="13" t="inlineStr">
@@ -3086,11 +3086,11 @@
         <v>-19</v>
       </c>
       <c r="I75" s="15" t="n">
-        <v>-27968000</v>
+        <v>-27967991</v>
       </c>
       <c r="J75" s="16" t="inlineStr">
         <is>
-          <t>4.92%→4.79%</t>
+          <t>5.12%→4.99%</t>
         </is>
       </c>
       <c r="K75" s="13" t="inlineStr">
@@ -3109,11 +3109,11 @@
         <v>11</v>
       </c>
       <c r="C76" s="11" t="n">
-        <v>23936000</v>
+        <v>23900793</v>
       </c>
       <c r="D76" s="12" t="inlineStr">
         <is>
-          <t>7.22%→7.28%</t>
+          <t>7.51%→7.58%</t>
         </is>
       </c>
       <c r="E76" s="13" t="inlineStr">
@@ -3130,11 +3130,11 @@
         <v>-15</v>
       </c>
       <c r="I76" s="15" t="n">
-        <v>-61632000</v>
+        <v>-67967979</v>
       </c>
       <c r="J76" s="16" t="inlineStr">
         <is>
-          <t>1.45%→1.20%</t>
+          <t>1.67%→1.38%</t>
         </is>
       </c>
       <c r="K76" s="13" t="inlineStr">
@@ -3153,11 +3153,11 @@
         <v>10</v>
       </c>
       <c r="C77" s="11" t="n">
-        <v>42944000</v>
+        <v>39871988</v>
       </c>
       <c r="D77" s="12" t="inlineStr">
         <is>
-          <t>1.06%→1.22%</t>
+          <t>1.03%→1.19%</t>
         </is>
       </c>
       <c r="E77" s="13" t="inlineStr">
@@ -3174,11 +3174,11 @@
         <v>-6</v>
       </c>
       <c r="I77" s="15" t="n">
-        <v>-48115200</v>
+        <v>-45004786</v>
       </c>
       <c r="J77" s="16" t="inlineStr">
         <is>
-          <t>2.86%→2.66%</t>
+          <t>2.79%→2.60%</t>
         </is>
       </c>
       <c r="K77" s="13" t="inlineStr">
@@ -3190,23 +3190,23 @@
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B78" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>53804800</v>
+        <v>36377589</v>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>2.32%→2.52%</t>
+          <t>1.23%→1.38%</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>77→84</t>
+          <t>58→65</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
@@ -3218,7 +3218,7 @@
         <v>-3</v>
       </c>
       <c r="I78" s="15" t="n">
-        <v>-8313600</v>
+        <v>-7891198</v>
       </c>
       <c r="J78" s="16" t="inlineStr">
         <is>
@@ -3234,23 +3234,23 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B79" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>37408000</v>
+        <v>48742385</v>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>1.22%→1.36%</t>
+          <t>2.19%→2.38%</t>
         </is>
       </c>
       <c r="E79" s="13" t="inlineStr">
         <is>
-          <t>58→65</t>
+          <t>77→84</t>
         </is>
       </c>
       <c r="G79" s="17" t="n"/>
@@ -3269,7 +3269,7 @@
         <v>6</v>
       </c>
       <c r="C80" s="11" t="n">
-        <v>22963200</v>
+        <v>22348793</v>
       </c>
       <c r="D80" s="12" t="inlineStr">
         <is>
@@ -3324,7 +3324,7 @@
     <row r="86" ht="19" customHeight="1">
       <c r="A86" s="3" t="inlineStr">
         <is>
-          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 863억   ·   현금 2억(0.3%)      오늘 2026-10-23  vs  5일전 2026-10-16      매수 14종목  /  매도 18종목</t>
+          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 847억      오늘 2026-10-23  vs  5일전 2026-10-16      매수 14종목  /  매도 18종목</t>
         </is>
       </c>
       <c r="B86" s="4" t="n"/>
@@ -3420,7 +3420,7 @@
         <v>964</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>2147310000</v>
+        <v>2173337219</v>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
@@ -3441,7 +3441,7 @@
         <v>-430</v>
       </c>
       <c r="I89" s="15" t="n">
-        <v>-1014585000</v>
+        <v>-1026882631</v>
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>
@@ -3464,7 +3464,7 @@
         <v>256</v>
       </c>
       <c r="C90" s="11" t="n">
-        <v>1113024000</v>
+        <v>1126514795</v>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
@@ -3485,7 +3485,7 @@
         <v>-237</v>
       </c>
       <c r="I90" s="15" t="n">
-        <v>-521269650</v>
+        <v>-527587880</v>
       </c>
       <c r="J90" s="16" t="inlineStr">
         <is>
@@ -3508,7 +3508,7 @@
         <v>242</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>1110054000</v>
+        <v>1123508796</v>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
@@ -3529,7 +3529,7 @@
         <v>-223</v>
       </c>
       <c r="I91" s="15" t="n">
-        <v>-965868750</v>
+        <v>-977575899</v>
       </c>
       <c r="J91" s="16" t="inlineStr">
         <is>
@@ -3552,7 +3552,7 @@
         <v>235</v>
       </c>
       <c r="C92" s="11" t="n">
-        <v>587441250</v>
+        <v>594561536</v>
       </c>
       <c r="D92" s="12" t="inlineStr">
         <is>
@@ -3573,7 +3573,7 @@
         <v>-147</v>
       </c>
       <c r="I92" s="15" t="n">
-        <v>-636693750</v>
+        <v>-644411018</v>
       </c>
       <c r="J92" s="16" t="inlineStr">
         <is>
@@ -3596,7 +3596,7 @@
         <v>140</v>
       </c>
       <c r="C93" s="11" t="n">
-        <v>562485000</v>
+        <v>569302795</v>
       </c>
       <c r="D93" s="12" t="inlineStr">
         <is>
@@ -3617,7 +3617,7 @@
         <v>-133</v>
       </c>
       <c r="I93" s="15" t="n">
-        <v>-837201750</v>
+        <v>-847349346</v>
       </c>
       <c r="J93" s="16" t="inlineStr">
         <is>
@@ -3640,7 +3640,7 @@
         <v>95</v>
       </c>
       <c r="C94" s="11" t="n">
-        <v>630135000</v>
+        <v>637772771</v>
       </c>
       <c r="D94" s="12" t="inlineStr">
         <is>
@@ -3661,7 +3661,7 @@
         <v>-108</v>
       </c>
       <c r="I94" s="15" t="n">
-        <v>-282447000</v>
+        <v>-285870497</v>
       </c>
       <c r="J94" s="16" t="inlineStr">
         <is>
@@ -3684,7 +3684,7 @@
         <v>88</v>
       </c>
       <c r="C95" s="11" t="n">
-        <v>685344000</v>
+        <v>693650951</v>
       </c>
       <c r="D95" s="12" t="inlineStr">
         <is>
@@ -3705,7 +3705,7 @@
         <v>-108</v>
       </c>
       <c r="I95" s="15" t="n">
-        <v>-1258092000</v>
+        <v>-1273341143</v>
       </c>
       <c r="J95" s="16" t="inlineStr">
         <is>
@@ -3728,7 +3728,7 @@
         <v>85</v>
       </c>
       <c r="C96" s="11" t="n">
-        <v>488070000</v>
+        <v>493985823</v>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
@@ -3749,7 +3749,7 @@
         <v>-85</v>
       </c>
       <c r="I96" s="15" t="n">
-        <v>-295226250</v>
+        <v>-298804643</v>
       </c>
       <c r="J96" s="16" t="inlineStr">
         <is>
@@ -3772,7 +3772,7 @@
         <v>59</v>
       </c>
       <c r="C97" s="11" t="n">
-        <v>401082000</v>
+        <v>405943454</v>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
@@ -3793,7 +3793,7 @@
         <v>-57</v>
       </c>
       <c r="I97" s="15" t="n">
-        <v>-251583750</v>
+        <v>-254633159</v>
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
@@ -3809,23 +3809,23 @@
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="B98" s="11" t="n">
         <v>46</v>
       </c>
       <c r="C98" s="11" t="n">
-        <v>793914000</v>
+        <v>234300916</v>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>1.11%→1.99%</t>
+          <t>1.95%→2.35%</t>
         </is>
       </c>
       <c r="E98" s="13" t="inlineStr">
         <is>
-          <t>50→96</t>
+          <t>343→389</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -3837,7 +3837,7 @@
         <v>-49</v>
       </c>
       <c r="I98" s="15" t="n">
-        <v>-523908000</v>
+        <v>-530258209</v>
       </c>
       <c r="J98" s="16" t="inlineStr">
         <is>
@@ -3853,23 +3853,23 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B99" s="11" t="n">
         <v>46</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>231495000</v>
+        <v>803536911</v>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>1.95%→2.35%</t>
+          <t>1.11%→1.99%</t>
         </is>
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>343→389</t>
+          <t>50→96</t>
         </is>
       </c>
       <c r="G99" s="14" t="inlineStr">
@@ -3881,7 +3881,7 @@
         <v>-48</v>
       </c>
       <c r="I99" s="15" t="n">
-        <v>-946440000</v>
+        <v>-957911656</v>
       </c>
       <c r="J99" s="16" t="inlineStr">
         <is>
@@ -3904,7 +3904,7 @@
         <v>30</v>
       </c>
       <c r="C100" s="11" t="n">
-        <v>242797500</v>
+        <v>245740412</v>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
@@ -3925,7 +3925,7 @@
         <v>-41</v>
       </c>
       <c r="I100" s="15" t="n">
-        <v>-416047500</v>
+        <v>-421090349</v>
       </c>
       <c r="J100" s="16" t="inlineStr">
         <is>
@@ -3948,7 +3948,7 @@
         <v>21</v>
       </c>
       <c r="C101" s="11" t="n">
-        <v>222453000</v>
+        <v>225149319</v>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
@@ -3969,7 +3969,7 @@
         <v>-39</v>
       </c>
       <c r="I101" s="15" t="n">
-        <v>-429214500</v>
+        <v>-434416944</v>
       </c>
       <c r="J101" s="16" t="inlineStr">
         <is>
@@ -3992,7 +3992,7 @@
         <v>16</v>
       </c>
       <c r="C102" s="11" t="n">
-        <v>309408000</v>
+        <v>313158287</v>
       </c>
       <c r="D102" s="12" t="inlineStr">
         <is>
@@ -4013,7 +4013,7 @@
         <v>-7</v>
       </c>
       <c r="I102" s="15" t="n">
-        <v>-285862500</v>
+        <v>-289327396</v>
       </c>
       <c r="J102" s="16" t="inlineStr">
         <is>
@@ -4041,7 +4041,7 @@
         <v>-6</v>
       </c>
       <c r="I103" s="15" t="n">
-        <v>-214830000</v>
+        <v>-217433922</v>
       </c>
       <c r="J103" s="16" t="inlineStr">
         <is>
@@ -4069,7 +4069,7 @@
         <v>-5</v>
       </c>
       <c r="I104" s="15" t="n">
-        <v>-139012500</v>
+        <v>-140697449</v>
       </c>
       <c r="J104" s="16" t="inlineStr">
         <is>
@@ -4090,23 +4090,23 @@
       <c r="E105" s="17" t="n"/>
       <c r="G105" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H105" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I105" s="15" t="n">
-        <v>-270600000</v>
+        <v>-170005939</v>
       </c>
       <c r="J105" s="16" t="inlineStr">
         <is>
-          <t>4.48%→3.97%</t>
+          <t>2.50%→2.11%</t>
         </is>
       </c>
       <c r="K105" s="13" t="inlineStr">
         <is>
-          <t>53→49</t>
+          <t>46→42</t>
         </is>
       </c>
     </row>
@@ -4118,23 +4118,23 @@
       <c r="E106" s="17" t="n"/>
       <c r="G106" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H106" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I106" s="15" t="n">
-        <v>-167970000</v>
+        <v>-273879902</v>
       </c>
       <c r="J106" s="16" t="inlineStr">
         <is>
-          <t>2.50%→2.11%</t>
+          <t>4.48%→3.97%</t>
         </is>
       </c>
       <c r="K106" s="13" t="inlineStr">
         <is>
-          <t>46→42</t>
+          <t>53→49</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261023.xlsx
+++ b/reports/pdf_rolling5_20261023.xlsx
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>586245635</v>
+        <v>2958120178</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>0.46%→0.52%</t>
+          <t>1.50%→2.10%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>34→46</t>
+          <t>25→37</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1258,23 +1258,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>2958120178</v>
+        <v>586245635</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>1.50%→2.10%</t>
+          <t>0.46%→0.52%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>25→37</t>
+          <t>34→46</t>
         </is>
       </c>
       <c r="G20" s="17" t="n"/>
@@ -2021,23 +2021,23 @@
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀  (편출)</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-765599582</v>
+        <v>-2653198553</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.00%</t>
+          <t>4.06%→3.16%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>180→130</t>
         </is>
       </c>
     </row>
@@ -2065,18 +2065,18 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠  (편출)</t>
+          <t>비츠로셀  (편출)</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-1841398996</v>
+        <v>-765599582</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>0.83%→0.00%</t>
+          <t>0.34%→0.00%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
@@ -2109,23 +2109,23 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에이치브이엠  (편출)</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-2653198553</v>
+        <v>-1841398996</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>4.06%→3.16%</t>
+          <t>0.83%→0.00%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>180→130</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -2397,23 +2397,23 @@
       <c r="E53" s="17" t="n"/>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-1092959404</v>
+        <v>-4329597638</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>3.18%→2.29%</t>
+          <t>5.76%→3.72%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>89→73</t>
+          <t>46→30</t>
         </is>
       </c>
     </row>
@@ -2425,23 +2425,23 @@
       <c r="E54" s="17" t="n"/>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-4329597638</v>
+        <v>-1092959404</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>5.76%→3.72%</t>
+          <t>3.18%→2.29%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>46→30</t>
+          <t>89→73</t>
         </is>
       </c>
     </row>
@@ -2481,23 +2481,23 @@
       <c r="E56" s="17" t="n"/>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>보로노이  (편출)</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-1927198949</v>
+        <v>-598223674</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>2.76%→2.10%</t>
+          <t>0.27%→0.00%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>27→19</t>
+          <t>8→0</t>
         </is>
       </c>
     </row>
@@ -2509,23 +2509,23 @@
       <c r="E57" s="17" t="n"/>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>보로노이  (편출)</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-598223674</v>
+        <v>-1927198949</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.00%</t>
+          <t>2.76%→2.10%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>8→0</t>
+          <t>27→19</t>
         </is>
       </c>
     </row>
@@ -3190,23 +3190,23 @@
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B78" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>36377589</v>
+        <v>48742385</v>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>1.23%→1.38%</t>
+          <t>2.19%→2.38%</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>58→65</t>
+          <t>77→84</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
@@ -3234,23 +3234,23 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B79" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>48742385</v>
+        <v>36377589</v>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>2.19%→2.38%</t>
+          <t>1.23%→1.38%</t>
         </is>
       </c>
       <c r="E79" s="13" t="inlineStr">
         <is>
-          <t>77→84</t>
+          <t>58→65</t>
         </is>
       </c>
       <c r="G79" s="17" t="n"/>
@@ -3654,23 +3654,23 @@
       </c>
       <c r="G94" s="14" t="inlineStr">
         <is>
-          <t>네오셈</t>
+          <t>씨엠티엑스  (편출)</t>
         </is>
       </c>
       <c r="H94" s="15" t="n">
         <v>-108</v>
       </c>
       <c r="I94" s="15" t="n">
-        <v>-285870497</v>
+        <v>-1273341143</v>
       </c>
       <c r="J94" s="16" t="inlineStr">
         <is>
-          <t>2.09%→2.16%</t>
+          <t>1.52%→0.00%</t>
         </is>
       </c>
       <c r="K94" s="13" t="inlineStr">
         <is>
-          <t>797→689</t>
+          <t>108→0</t>
         </is>
       </c>
     </row>
@@ -3698,23 +3698,23 @@
       </c>
       <c r="G95" s="14" t="inlineStr">
         <is>
-          <t>씨엠티엑스  (편출)</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="H95" s="15" t="n">
         <v>-108</v>
       </c>
       <c r="I95" s="15" t="n">
-        <v>-1273341143</v>
+        <v>-285870497</v>
       </c>
       <c r="J95" s="16" t="inlineStr">
         <is>
-          <t>1.52%→0.00%</t>
+          <t>2.09%→2.16%</t>
         </is>
       </c>
       <c r="K95" s="13" t="inlineStr">
         <is>
-          <t>108→0</t>
+          <t>797→689</t>
         </is>
       </c>
     </row>
@@ -4090,23 +4090,23 @@
       <c r="E105" s="17" t="n"/>
       <c r="G105" s="14" t="inlineStr">
         <is>
-          <t>티에스이</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H105" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I105" s="15" t="n">
-        <v>-170005939</v>
+        <v>-273879902</v>
       </c>
       <c r="J105" s="16" t="inlineStr">
         <is>
-          <t>2.50%→2.11%</t>
+          <t>4.48%→3.97%</t>
         </is>
       </c>
       <c r="K105" s="13" t="inlineStr">
         <is>
-          <t>46→42</t>
+          <t>53→49</t>
         </is>
       </c>
     </row>
@@ -4118,23 +4118,23 @@
       <c r="E106" s="17" t="n"/>
       <c r="G106" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>티에스이</t>
         </is>
       </c>
       <c r="H106" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I106" s="15" t="n">
-        <v>-273879902</v>
+        <v>-170005939</v>
       </c>
       <c r="J106" s="16" t="inlineStr">
         <is>
-          <t>4.48%→3.97%</t>
+          <t>2.50%→2.11%</t>
         </is>
       </c>
       <c r="K106" s="13" t="inlineStr">
         <is>
-          <t>53→49</t>
+          <t>46→42</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261023.xlsx
+++ b/reports/pdf_rolling5_20261023.xlsx
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2958120178</v>
+        <v>413539225</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.50%→2.10%</t>
+          <t>1.47%→1.46%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>25→37</t>
+          <t>173→185</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1230,23 +1230,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>413539225</v>
+        <v>2958120178</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>1.47%→1.46%</t>
+          <t>1.50%→2.10%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>173→185</t>
+          <t>25→37</t>
         </is>
       </c>
       <c r="G19" s="17" t="n"/>
@@ -2021,23 +2021,23 @@
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>비츠로셀  (편출)</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-2653198553</v>
+        <v>-765599582</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>4.06%→3.16%</t>
+          <t>0.34%→0.00%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>180→130</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -2065,18 +2065,18 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀  (편출)</t>
+          <t>에이치브이엠  (편출)</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-765599582</v>
+        <v>-1841398996</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.00%</t>
+          <t>0.83%→0.00%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
@@ -2109,23 +2109,23 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠  (편출)</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-1841398996</v>
+        <v>-2653198553</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>0.83%→0.00%</t>
+          <t>4.06%→3.16%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>180→130</t>
         </is>
       </c>
     </row>
@@ -2397,23 +2397,23 @@
       <c r="E53" s="17" t="n"/>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-4329597638</v>
+        <v>-1092959404</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>5.76%→3.72%</t>
+          <t>3.18%→2.29%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>46→30</t>
+          <t>89→73</t>
         </is>
       </c>
     </row>
@@ -2425,23 +2425,23 @@
       <c r="E54" s="17" t="n"/>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-1092959404</v>
+        <v>-4329597638</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>3.18%→2.29%</t>
+          <t>5.76%→3.72%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>89→73</t>
+          <t>46→30</t>
         </is>
       </c>
     </row>
@@ -2481,23 +2481,23 @@
       <c r="E56" s="17" t="n"/>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>보로노이  (편출)</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-598223674</v>
+        <v>-1927198949</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.00%</t>
+          <t>2.76%→2.10%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>8→0</t>
+          <t>27→19</t>
         </is>
       </c>
     </row>
@@ -2509,23 +2509,23 @@
       <c r="E57" s="17" t="n"/>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>보로노이  (편출)</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-1927198949</v>
+        <v>-598223674</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>2.76%→2.10%</t>
+          <t>0.27%→0.00%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>27→19</t>
+          <t>8→0</t>
         </is>
       </c>
     </row>
@@ -3190,23 +3190,23 @@
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B78" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>48742385</v>
+        <v>36377589</v>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>2.19%→2.38%</t>
+          <t>1.23%→1.38%</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>77→84</t>
+          <t>58→65</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
@@ -3234,23 +3234,23 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B79" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>36377589</v>
+        <v>48742385</v>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>1.23%→1.38%</t>
+          <t>2.19%→2.38%</t>
         </is>
       </c>
       <c r="E79" s="13" t="inlineStr">
         <is>
-          <t>58→65</t>
+          <t>77→84</t>
         </is>
       </c>
       <c r="G79" s="17" t="n"/>
@@ -3654,23 +3654,23 @@
       </c>
       <c r="G94" s="14" t="inlineStr">
         <is>
-          <t>씨엠티엑스  (편출)</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="H94" s="15" t="n">
         <v>-108</v>
       </c>
       <c r="I94" s="15" t="n">
-        <v>-1273341143</v>
+        <v>-285870497</v>
       </c>
       <c r="J94" s="16" t="inlineStr">
         <is>
-          <t>1.52%→0.00%</t>
+          <t>2.09%→2.16%</t>
         </is>
       </c>
       <c r="K94" s="13" t="inlineStr">
         <is>
-          <t>108→0</t>
+          <t>797→689</t>
         </is>
       </c>
     </row>
@@ -3698,23 +3698,23 @@
       </c>
       <c r="G95" s="14" t="inlineStr">
         <is>
-          <t>네오셈</t>
+          <t>씨엠티엑스  (편출)</t>
         </is>
       </c>
       <c r="H95" s="15" t="n">
         <v>-108</v>
       </c>
       <c r="I95" s="15" t="n">
-        <v>-285870497</v>
+        <v>-1273341143</v>
       </c>
       <c r="J95" s="16" t="inlineStr">
         <is>
-          <t>2.09%→2.16%</t>
+          <t>1.52%→0.00%</t>
         </is>
       </c>
       <c r="K95" s="13" t="inlineStr">
         <is>
-          <t>797→689</t>
+          <t>108→0</t>
         </is>
       </c>
     </row>

--- a/reports/pdf_rolling5_20261023.xlsx
+++ b/reports/pdf_rolling5_20261023.xlsx
@@ -2021,23 +2021,23 @@
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀  (편출)</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-765599582</v>
+        <v>-2653198553</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.00%</t>
+          <t>4.06%→3.16%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>180→130</t>
         </is>
       </c>
     </row>
@@ -2065,18 +2065,18 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠  (편출)</t>
+          <t>비츠로셀  (편출)</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-1841398996</v>
+        <v>-765599582</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>0.83%→0.00%</t>
+          <t>0.34%→0.00%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
@@ -2109,23 +2109,23 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>에이치브이엠  (편출)</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-2653198553</v>
+        <v>-1841398996</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>4.06%→3.16%</t>
+          <t>0.83%→0.00%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>180→130</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -2481,23 +2481,23 @@
       <c r="E56" s="17" t="n"/>
       <c r="G56" s="14" t="inlineStr">
         <is>
-          <t>레인보우로보틱스</t>
+          <t>보로노이  (편출)</t>
         </is>
       </c>
       <c r="H56" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I56" s="15" t="n">
-        <v>-1927198949</v>
+        <v>-598223674</v>
       </c>
       <c r="J56" s="16" t="inlineStr">
         <is>
-          <t>2.76%→2.10%</t>
+          <t>0.27%→0.00%</t>
         </is>
       </c>
       <c r="K56" s="13" t="inlineStr">
         <is>
-          <t>27→19</t>
+          <t>8→0</t>
         </is>
       </c>
     </row>
@@ -2509,23 +2509,23 @@
       <c r="E57" s="17" t="n"/>
       <c r="G57" s="14" t="inlineStr">
         <is>
-          <t>보로노이  (편출)</t>
+          <t>레인보우로보틱스</t>
         </is>
       </c>
       <c r="H57" s="15" t="n">
         <v>-8</v>
       </c>
       <c r="I57" s="15" t="n">
-        <v>-598223674</v>
+        <v>-1927198949</v>
       </c>
       <c r="J57" s="16" t="inlineStr">
         <is>
-          <t>0.27%→0.00%</t>
+          <t>2.76%→2.10%</t>
         </is>
       </c>
       <c r="K57" s="13" t="inlineStr">
         <is>
-          <t>8→0</t>
+          <t>27→19</t>
         </is>
       </c>
     </row>
@@ -3190,23 +3190,23 @@
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B78" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>36377589</v>
+        <v>48742385</v>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>1.23%→1.38%</t>
+          <t>2.19%→2.38%</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>58→65</t>
+          <t>77→84</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
@@ -3234,23 +3234,23 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B79" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>48742385</v>
+        <v>36377589</v>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>2.19%→2.38%</t>
+          <t>1.23%→1.38%</t>
         </is>
       </c>
       <c r="E79" s="13" t="inlineStr">
         <is>
-          <t>77→84</t>
+          <t>58→65</t>
         </is>
       </c>
       <c r="G79" s="17" t="n"/>
@@ -3809,23 +3809,23 @@
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B98" s="11" t="n">
         <v>46</v>
       </c>
       <c r="C98" s="11" t="n">
-        <v>234300916</v>
+        <v>803536911</v>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>1.95%→2.35%</t>
+          <t>1.11%→1.99%</t>
         </is>
       </c>
       <c r="E98" s="13" t="inlineStr">
         <is>
-          <t>343→389</t>
+          <t>50→96</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
@@ -3853,23 +3853,23 @@
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="B99" s="11" t="n">
         <v>46</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>803536911</v>
+        <v>234300916</v>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>1.11%→1.99%</t>
+          <t>1.95%→2.35%</t>
         </is>
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>50→96</t>
+          <t>343→389</t>
         </is>
       </c>
       <c r="G99" s="14" t="inlineStr">

--- a/reports/pdf_rolling5_20261023.xlsx
+++ b/reports/pdf_rolling5_20261023.xlsx
@@ -536,7 +536,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:K110"/>
+  <dimension ref="A1:K149"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="18" customWidth="1" min="1" max="1"/>
@@ -562,7 +562,7 @@
     <row r="2">
       <c r="A2" s="2" t="inlineStr">
         <is>
-          <t>최근 5거래일 변화  ·  2026-10-16 ~ 2026-10-23  (최근 5거래일)  ·  캡처 6/10  ·  대기: RISE, TIGER, TIGER, MIDAS</t>
+          <t>최근 5거래일 변화  ·  2026-10-16 ~ 2026-10-23  (최근 5거래일)  ·  캡처 9/10  ·  대기: RISE</t>
         </is>
       </c>
     </row>
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>413539225</v>
+        <v>2958120178</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.47%→1.46%</t>
+          <t>1.50%→2.10%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>173→185</t>
+          <t>25→37</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1230,23 +1230,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>2958120178</v>
+        <v>586245635</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>1.50%→2.10%</t>
+          <t>0.46%→0.52%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>25→37</t>
+          <t>34→46</t>
         </is>
       </c>
       <c r="G19" s="17" t="n"/>
@@ -1258,23 +1258,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>586245635</v>
+        <v>413539225</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>0.46%→0.52%</t>
+          <t>1.47%→1.46%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>34→46</t>
+          <t>173→185</t>
         </is>
       </c>
       <c r="G20" s="17" t="n"/>
@@ -2065,18 +2065,18 @@
       </c>
       <c r="G44" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀  (편출)</t>
+          <t>에이치브이엠  (편출)</t>
         </is>
       </c>
       <c r="H44" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I44" s="15" t="n">
-        <v>-765599582</v>
+        <v>-1841398996</v>
       </c>
       <c r="J44" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.00%</t>
+          <t>0.83%→0.00%</t>
         </is>
       </c>
       <c r="K44" s="13" t="inlineStr">
@@ -2109,18 +2109,18 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>에이치브이엠  (편출)</t>
+          <t>비츠로셀  (편출)</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-1841398996</v>
+        <v>-765599582</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>0.83%→0.00%</t>
+          <t>0.34%→0.00%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
@@ -2397,23 +2397,23 @@
       <c r="E53" s="17" t="n"/>
       <c r="G53" s="14" t="inlineStr">
         <is>
-          <t>두산테스나</t>
+          <t>이오테크닉스</t>
         </is>
       </c>
       <c r="H53" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I53" s="15" t="n">
-        <v>-1092959404</v>
+        <v>-4329597638</v>
       </c>
       <c r="J53" s="16" t="inlineStr">
         <is>
-          <t>3.18%→2.29%</t>
+          <t>5.76%→3.72%</t>
         </is>
       </c>
       <c r="K53" s="13" t="inlineStr">
         <is>
-          <t>89→73</t>
+          <t>46→30</t>
         </is>
       </c>
     </row>
@@ -2425,23 +2425,23 @@
       <c r="E54" s="17" t="n"/>
       <c r="G54" s="14" t="inlineStr">
         <is>
-          <t>이오테크닉스</t>
+          <t>두산테스나</t>
         </is>
       </c>
       <c r="H54" s="15" t="n">
         <v>-16</v>
       </c>
       <c r="I54" s="15" t="n">
-        <v>-4329597638</v>
+        <v>-1092959404</v>
       </c>
       <c r="J54" s="16" t="inlineStr">
         <is>
-          <t>5.76%→3.72%</t>
+          <t>3.18%→2.29%</t>
         </is>
       </c>
       <c r="K54" s="13" t="inlineStr">
         <is>
-          <t>46→30</t>
+          <t>89→73</t>
         </is>
       </c>
     </row>
@@ -3190,23 +3190,23 @@
     <row r="78">
       <c r="A78" s="10" t="inlineStr">
         <is>
-          <t>테스</t>
+          <t>선익시스템</t>
         </is>
       </c>
       <c r="B78" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C78" s="11" t="n">
-        <v>48742385</v>
+        <v>36377589</v>
       </c>
       <c r="D78" s="12" t="inlineStr">
         <is>
-          <t>2.19%→2.38%</t>
+          <t>1.23%→1.38%</t>
         </is>
       </c>
       <c r="E78" s="13" t="inlineStr">
         <is>
-          <t>77→84</t>
+          <t>58→65</t>
         </is>
       </c>
       <c r="G78" s="14" t="inlineStr">
@@ -3234,23 +3234,23 @@
     <row r="79">
       <c r="A79" s="10" t="inlineStr">
         <is>
-          <t>선익시스템</t>
+          <t>테스</t>
         </is>
       </c>
       <c r="B79" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C79" s="11" t="n">
-        <v>36377589</v>
+        <v>48742385</v>
       </c>
       <c r="D79" s="12" t="inlineStr">
         <is>
-          <t>1.23%→1.38%</t>
+          <t>2.19%→2.38%</t>
         </is>
       </c>
       <c r="E79" s="13" t="inlineStr">
         <is>
-          <t>58→65</t>
+          <t>77→84</t>
         </is>
       </c>
       <c r="G79" s="17" t="n"/>
@@ -3305,899 +3305,2381 @@
       <c r="K82" s="19" t="n"/>
     </row>
     <row r="84" ht="19" customHeight="1">
-      <c r="A84" s="18" t="inlineStr">
-        <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B84" s="19" t="n"/>
-      <c r="C84" s="19" t="n"/>
-      <c r="D84" s="19" t="n"/>
-      <c r="E84" s="19" t="n"/>
-      <c r="F84" s="19" t="n"/>
-      <c r="G84" s="19" t="n"/>
-      <c r="H84" s="19" t="n"/>
-      <c r="I84" s="19" t="n"/>
-      <c r="J84" s="19" t="n"/>
-      <c r="K84" s="19" t="n"/>
-    </row>
-    <row r="86" ht="19" customHeight="1">
-      <c r="A86" s="3" t="inlineStr">
-        <is>
-          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 847억      오늘 2026-10-23  vs  5일전 2026-10-16      매수 14종목  /  매도 18종목</t>
-        </is>
-      </c>
-      <c r="B86" s="4" t="n"/>
-      <c r="C86" s="4" t="n"/>
-      <c r="D86" s="4" t="n"/>
-      <c r="E86" s="4" t="n"/>
-      <c r="F86" s="4" t="n"/>
-      <c r="G86" s="4" t="n"/>
-      <c r="H86" s="4" t="n"/>
-      <c r="I86" s="4" t="n"/>
-      <c r="J86" s="4" t="n"/>
-      <c r="K86" s="4" t="n"/>
+      <c r="A84" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,073억   ·   현금 50억(4.7%)      오늘 2026-10-23  vs  5일전 2026-10-16      매수 5종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B84" s="4" t="n"/>
+      <c r="C84" s="4" t="n"/>
+      <c r="D84" s="4" t="n"/>
+      <c r="E84" s="4" t="n"/>
+      <c r="F84" s="4" t="n"/>
+      <c r="G84" s="4" t="n"/>
+      <c r="H84" s="4" t="n"/>
+      <c r="I84" s="4" t="n"/>
+      <c r="J84" s="4" t="n"/>
+      <c r="K84" s="4" t="n"/>
+    </row>
+    <row r="85">
+      <c r="A85" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B85" s="6" t="n"/>
+      <c r="C85" s="6" t="n"/>
+      <c r="D85" s="6" t="n"/>
+      <c r="E85" s="6" t="n"/>
+      <c r="G85" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H85" s="8" t="n"/>
+      <c r="I85" s="8" t="n"/>
+      <c r="J85" s="8" t="n"/>
+      <c r="K85" s="8" t="n"/>
+    </row>
+    <row r="86">
+      <c r="A86" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B86" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C86" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D86" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E86" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G86" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H86" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I86" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J86" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K86" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
     </row>
     <row r="87">
-      <c r="A87" s="5" t="inlineStr">
-        <is>
-          <t>🔴 매수 (확대·신규편입)</t>
-        </is>
-      </c>
-      <c r="B87" s="6" t="n"/>
-      <c r="C87" s="6" t="n"/>
-      <c r="D87" s="6" t="n"/>
-      <c r="E87" s="6" t="n"/>
-      <c r="G87" s="7" t="inlineStr">
-        <is>
-          <t>🔵 매도 (축소·편출)</t>
-        </is>
-      </c>
-      <c r="H87" s="8" t="n"/>
-      <c r="I87" s="8" t="n"/>
-      <c r="J87" s="8" t="n"/>
-      <c r="K87" s="8" t="n"/>
+      <c r="A87" s="10" t="inlineStr">
+        <is>
+          <t>HLB이노베이션</t>
+        </is>
+      </c>
+      <c r="B87" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C87" s="11" t="n">
+        <v>197992021</v>
+      </c>
+      <c r="D87" s="12" t="inlineStr">
+        <is>
+          <t>3.10%→2.42%</t>
+        </is>
+      </c>
+      <c r="E87" s="13" t="inlineStr">
+        <is>
+          <t>69→75</t>
+        </is>
+      </c>
+      <c r="G87" s="14" t="inlineStr">
+        <is>
+          <t>와이바이오로직스</t>
+        </is>
+      </c>
+      <c r="H87" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I87" s="15" t="n">
+        <v>-73311907</v>
+      </c>
+      <c r="J87" s="16" t="inlineStr">
+        <is>
+          <t>0.37%→0.20%</t>
+        </is>
+      </c>
+      <c r="K87" s="13" t="inlineStr">
+        <is>
+          <t>15→11</t>
+        </is>
+      </c>
     </row>
     <row r="88">
-      <c r="A88" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="B88" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="C88" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="D88" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="E88" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
-        </is>
-      </c>
-      <c r="G88" s="9" t="inlineStr">
-        <is>
-          <t>종목명</t>
-        </is>
-      </c>
-      <c r="H88" s="9" t="inlineStr">
-        <is>
-          <t>변화(1CU주)</t>
-        </is>
-      </c>
-      <c r="I88" s="9" t="inlineStr">
-        <is>
-          <t>전체매매금액(원)</t>
-        </is>
-      </c>
-      <c r="J88" s="9" t="inlineStr">
-        <is>
-          <t>보유비중(전→당)</t>
-        </is>
-      </c>
-      <c r="K88" s="9" t="inlineStr">
-        <is>
-          <t>전일→당일</t>
+      <c r="A88" s="10" t="inlineStr">
+        <is>
+          <t>쓰리빌리언</t>
+        </is>
+      </c>
+      <c r="B88" s="11" t="n">
+        <v>6</v>
+      </c>
+      <c r="C88" s="11" t="n">
+        <v>65706420</v>
+      </c>
+      <c r="D88" s="12" t="inlineStr">
+        <is>
+          <t>1.48%→1.12%</t>
+        </is>
+      </c>
+      <c r="E88" s="13" t="inlineStr">
+        <is>
+          <t>99→105</t>
+        </is>
+      </c>
+      <c r="G88" s="14" t="inlineStr">
+        <is>
+          <t>오름테라퓨틱</t>
+        </is>
+      </c>
+      <c r="H88" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I88" s="15" t="n">
+        <v>-105604057</v>
+      </c>
+      <c r="J88" s="16" t="inlineStr">
+        <is>
+          <t>0.43%→0.21%</t>
+        </is>
+      </c>
+      <c r="K88" s="13" t="inlineStr">
+        <is>
+          <t>9→6</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" s="10" t="inlineStr">
         <is>
-          <t>뉴파워프라즈마</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B89" s="11" t="n">
-        <v>964</v>
+        <v>5</v>
       </c>
       <c r="C89" s="11" t="n">
-        <v>2173337219</v>
+        <v>256633235</v>
       </c>
       <c r="D89" s="12" t="inlineStr">
         <is>
-          <t>0.87%→3.65%</t>
+          <t>7.06%→5.32%</t>
         </is>
       </c>
       <c r="E89" s="13" t="inlineStr">
         <is>
-          <t>403→1,367</t>
+          <t>101→106</t>
         </is>
       </c>
       <c r="G89" s="14" t="inlineStr">
         <is>
-          <t>엠케이전자</t>
+          <t>리가켐바이오</t>
         </is>
       </c>
       <c r="H89" s="15" t="n">
-        <v>-430</v>
+        <v>-3</v>
       </c>
       <c r="I89" s="15" t="n">
-        <v>-1026882631</v>
+        <v>-432639996</v>
       </c>
       <c r="J89" s="16" t="inlineStr">
         <is>
-          <t>3.43%→2.00%</t>
+          <t>7.86%→5.22%</t>
         </is>
       </c>
       <c r="K89" s="13" t="inlineStr">
         <is>
-          <t>1,137→707</t>
+          <t>40→37</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" s="10" t="inlineStr">
         <is>
-          <t>에프에스티  (신규)</t>
+          <t>프로티나</t>
         </is>
       </c>
       <c r="B90" s="11" t="n">
-        <v>256</v>
+        <v>4</v>
       </c>
       <c r="C90" s="11" t="n">
-        <v>1126514795</v>
+        <v>355338325</v>
       </c>
       <c r="D90" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.33%</t>
+          <t>2.54%→2.17%</t>
         </is>
       </c>
       <c r="E90" s="13" t="inlineStr">
         <is>
-          <t>0→256</t>
-        </is>
-      </c>
-      <c r="G90" s="14" t="inlineStr">
-        <is>
-          <t>저스템</t>
-        </is>
-      </c>
-      <c r="H90" s="15" t="n">
-        <v>-237</v>
-      </c>
-      <c r="I90" s="15" t="n">
-        <v>-527587880</v>
-      </c>
-      <c r="J90" s="16" t="inlineStr">
-        <is>
-          <t>2.89%→1.86%</t>
-        </is>
-      </c>
-      <c r="K90" s="13" t="inlineStr">
-        <is>
-          <t>942→705</t>
-        </is>
-      </c>
+          <t>21→25</t>
+        </is>
+      </c>
+      <c r="G90" s="17" t="n"/>
+      <c r="H90" s="17" t="n"/>
+      <c r="I90" s="17" t="n"/>
+      <c r="J90" s="17" t="n"/>
+      <c r="K90" s="17" t="n"/>
     </row>
     <row r="91">
       <c r="A91" s="10" t="inlineStr">
         <is>
-          <t>에스티아이</t>
+          <t>에이비엘바이오</t>
         </is>
       </c>
       <c r="B91" s="11" t="n">
-        <v>242</v>
+        <v>3</v>
       </c>
       <c r="C91" s="11" t="n">
-        <v>1123508796</v>
+        <v>277413254</v>
       </c>
       <c r="D91" s="12" t="inlineStr">
         <is>
-          <t>1.56%→2.93%</t>
+          <t>6.93%→5.24%</t>
         </is>
       </c>
       <c r="E91" s="13" t="inlineStr">
         <is>
-          <t>290→532</t>
-        </is>
-      </c>
-      <c r="G91" s="14" t="inlineStr">
-        <is>
-          <t>SFA</t>
-        </is>
-      </c>
-      <c r="H91" s="15" t="n">
-        <v>-223</v>
-      </c>
-      <c r="I91" s="15" t="n">
-        <v>-977575899</v>
-      </c>
-      <c r="J91" s="16" t="inlineStr">
-        <is>
-          <t>1.79%→0.50%</t>
-        </is>
-      </c>
-      <c r="K91" s="13" t="inlineStr">
-        <is>
-          <t>320→97</t>
-        </is>
-      </c>
-    </row>
-    <row r="92">
-      <c r="A92" s="10" t="inlineStr">
-        <is>
-          <t>샘씨엔에스</t>
-        </is>
-      </c>
-      <c r="B92" s="11" t="n">
-        <v>235</v>
-      </c>
-      <c r="C92" s="11" t="n">
-        <v>594561536</v>
-      </c>
-      <c r="D92" s="12" t="inlineStr">
-        <is>
-          <t>4.26%→5.06%</t>
-        </is>
-      </c>
-      <c r="E92" s="13" t="inlineStr">
-        <is>
-          <t>1,454→1,689</t>
-        </is>
-      </c>
-      <c r="G92" s="14" t="inlineStr">
-        <is>
-          <t>태웅</t>
-        </is>
-      </c>
-      <c r="H92" s="15" t="n">
-        <v>-147</v>
-      </c>
-      <c r="I92" s="15" t="n">
-        <v>-644411018</v>
-      </c>
-      <c r="J92" s="16" t="inlineStr">
-        <is>
-          <t>1.05%→0.20%</t>
-        </is>
-      </c>
-      <c r="K92" s="13" t="inlineStr">
-        <is>
-          <t>186→39</t>
-        </is>
-      </c>
-    </row>
-    <row r="93">
-      <c r="A93" s="10" t="inlineStr">
-        <is>
-          <t>코미코</t>
-        </is>
-      </c>
-      <c r="B93" s="11" t="n">
-        <v>140</v>
-      </c>
-      <c r="C93" s="11" t="n">
-        <v>569302795</v>
-      </c>
-      <c r="D93" s="12" t="inlineStr">
-        <is>
-          <t>1.28%→1.92%</t>
-        </is>
-      </c>
-      <c r="E93" s="13" t="inlineStr">
-        <is>
-          <t>259→399</t>
-        </is>
-      </c>
-      <c r="G93" s="14" t="inlineStr">
-        <is>
-          <t>코세스</t>
-        </is>
-      </c>
-      <c r="H93" s="15" t="n">
-        <v>-133</v>
-      </c>
-      <c r="I93" s="15" t="n">
-        <v>-847349346</v>
-      </c>
-      <c r="J93" s="16" t="inlineStr">
-        <is>
-          <t>3.83%→4.27%</t>
-        </is>
-      </c>
-      <c r="K93" s="13" t="inlineStr">
-        <is>
-          <t>699→566</t>
-        </is>
-      </c>
+          <t>55→58</t>
+        </is>
+      </c>
+      <c r="G91" s="17" t="n"/>
+      <c r="H91" s="17" t="n"/>
+      <c r="I91" s="17" t="n"/>
+      <c r="J91" s="17" t="n"/>
+      <c r="K91" s="17" t="n"/>
+    </row>
+    <row r="93" ht="19" customHeight="1">
+      <c r="A93" s="3" t="inlineStr">
+        <is>
+          <t>■ DS 코스닥액티브  (DS)      순자산 ≈ 847억      오늘 2026-10-23  vs  5일전 2026-10-16      매수 14종목  /  매도 18종목</t>
+        </is>
+      </c>
+      <c r="B93" s="4" t="n"/>
+      <c r="C93" s="4" t="n"/>
+      <c r="D93" s="4" t="n"/>
+      <c r="E93" s="4" t="n"/>
+      <c r="F93" s="4" t="n"/>
+      <c r="G93" s="4" t="n"/>
+      <c r="H93" s="4" t="n"/>
+      <c r="I93" s="4" t="n"/>
+      <c r="J93" s="4" t="n"/>
+      <c r="K93" s="4" t="n"/>
     </row>
     <row r="94">
-      <c r="A94" s="10" t="inlineStr">
-        <is>
-          <t>동진쎄미켐</t>
-        </is>
-      </c>
-      <c r="B94" s="11" t="n">
-        <v>95</v>
-      </c>
-      <c r="C94" s="11" t="n">
-        <v>637772771</v>
-      </c>
-      <c r="D94" s="12" t="inlineStr">
-        <is>
-          <t>2.23%→2.94%</t>
-        </is>
-      </c>
-      <c r="E94" s="13" t="inlineStr">
-        <is>
-          <t>275→370</t>
-        </is>
-      </c>
-      <c r="G94" s="14" t="inlineStr">
-        <is>
-          <t>네오셈</t>
-        </is>
-      </c>
-      <c r="H94" s="15" t="n">
-        <v>-108</v>
-      </c>
-      <c r="I94" s="15" t="n">
-        <v>-285870497</v>
-      </c>
-      <c r="J94" s="16" t="inlineStr">
-        <is>
-          <t>2.09%→2.16%</t>
-        </is>
-      </c>
-      <c r="K94" s="13" t="inlineStr">
-        <is>
-          <t>797→689</t>
-        </is>
-      </c>
+      <c r="A94" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B94" s="6" t="n"/>
+      <c r="C94" s="6" t="n"/>
+      <c r="D94" s="6" t="n"/>
+      <c r="E94" s="6" t="n"/>
+      <c r="G94" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H94" s="8" t="n"/>
+      <c r="I94" s="8" t="n"/>
+      <c r="J94" s="8" t="n"/>
+      <c r="K94" s="8" t="n"/>
     </row>
     <row r="95">
-      <c r="A95" s="10" t="inlineStr">
-        <is>
-          <t>RFHIC  (신규)</t>
-        </is>
-      </c>
-      <c r="B95" s="11" t="n">
-        <v>88</v>
-      </c>
-      <c r="C95" s="11" t="n">
-        <v>693650951</v>
-      </c>
-      <c r="D95" s="12" t="inlineStr">
-        <is>
-          <t>0.00%→0.82%</t>
-        </is>
-      </c>
-      <c r="E95" s="13" t="inlineStr">
-        <is>
-          <t>0→88</t>
-        </is>
-      </c>
-      <c r="G95" s="14" t="inlineStr">
-        <is>
-          <t>씨엠티엑스  (편출)</t>
-        </is>
-      </c>
-      <c r="H95" s="15" t="n">
-        <v>-108</v>
-      </c>
-      <c r="I95" s="15" t="n">
-        <v>-1273341143</v>
-      </c>
-      <c r="J95" s="16" t="inlineStr">
-        <is>
-          <t>1.52%→0.00%</t>
-        </is>
-      </c>
-      <c r="K95" s="13" t="inlineStr">
-        <is>
-          <t>108→0</t>
+      <c r="A95" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B95" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C95" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D95" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E95" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G95" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H95" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I95" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J95" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K95" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" s="10" t="inlineStr">
         <is>
-          <t>엘티씨</t>
+          <t>뉴파워프라즈마</t>
         </is>
       </c>
       <c r="B96" s="11" t="n">
-        <v>85</v>
+        <v>964</v>
       </c>
       <c r="C96" s="11" t="n">
-        <v>493985823</v>
+        <v>2173337219</v>
       </c>
       <c r="D96" s="12" t="inlineStr">
         <is>
-          <t>0.39%→1.02%</t>
+          <t>0.87%→3.65%</t>
         </is>
       </c>
       <c r="E96" s="13" t="inlineStr">
         <is>
-          <t>63→148</t>
+          <t>403→1,367</t>
         </is>
       </c>
       <c r="G96" s="14" t="inlineStr">
         <is>
-          <t>싸이맥스  (편출)</t>
+          <t>엠케이전자</t>
         </is>
       </c>
       <c r="H96" s="15" t="n">
-        <v>-85</v>
+        <v>-430</v>
       </c>
       <c r="I96" s="15" t="n">
-        <v>-298804643</v>
+        <v>-1026882631</v>
       </c>
       <c r="J96" s="16" t="inlineStr">
         <is>
-          <t>0.36%→0.00%</t>
+          <t>3.43%→2.00%</t>
         </is>
       </c>
       <c r="K96" s="13" t="inlineStr">
         <is>
-          <t>85→0</t>
+          <t>1,137→707</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" s="10" t="inlineStr">
         <is>
-          <t>이엔에프테크놀로지</t>
+          <t>에프에스티  (신규)</t>
         </is>
       </c>
       <c r="B97" s="11" t="n">
-        <v>59</v>
+        <v>256</v>
       </c>
       <c r="C97" s="11" t="n">
-        <v>405943454</v>
+        <v>1126514795</v>
       </c>
       <c r="D97" s="12" t="inlineStr">
         <is>
-          <t>2.89%→3.32%</t>
+          <t>0.00%→1.33%</t>
         </is>
       </c>
       <c r="E97" s="13" t="inlineStr">
         <is>
-          <t>349→408</t>
+          <t>0→256</t>
         </is>
       </c>
       <c r="G97" s="14" t="inlineStr">
         <is>
-          <t>원익QnC  (편출)</t>
+          <t>저스템</t>
         </is>
       </c>
       <c r="H97" s="15" t="n">
-        <v>-57</v>
+        <v>-237</v>
       </c>
       <c r="I97" s="15" t="n">
-        <v>-254633159</v>
+        <v>-527587880</v>
       </c>
       <c r="J97" s="16" t="inlineStr">
         <is>
-          <t>0.30%→0.00%</t>
+          <t>2.89%→1.86%</t>
         </is>
       </c>
       <c r="K97" s="13" t="inlineStr">
         <is>
-          <t>57→0</t>
+          <t>942→705</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>에스티아이</t>
         </is>
       </c>
       <c r="B98" s="11" t="n">
-        <v>46</v>
+        <v>242</v>
       </c>
       <c r="C98" s="11" t="n">
-        <v>803536911</v>
+        <v>1123508796</v>
       </c>
       <c r="D98" s="12" t="inlineStr">
         <is>
-          <t>1.11%→1.99%</t>
+          <t>1.56%→2.93%</t>
         </is>
       </c>
       <c r="E98" s="13" t="inlineStr">
         <is>
-          <t>50→96</t>
+          <t>290→532</t>
         </is>
       </c>
       <c r="G98" s="14" t="inlineStr">
         <is>
-          <t>제주반도체</t>
+          <t>SFA</t>
         </is>
       </c>
       <c r="H98" s="15" t="n">
-        <v>-49</v>
+        <v>-223</v>
       </c>
       <c r="I98" s="15" t="n">
-        <v>-530258209</v>
+        <v>-977575899</v>
       </c>
       <c r="J98" s="16" t="inlineStr">
         <is>
-          <t>1.10%→0.49%</t>
+          <t>1.79%→0.50%</t>
         </is>
       </c>
       <c r="K98" s="13" t="inlineStr">
         <is>
-          <t>87→38</t>
+          <t>320→97</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" s="10" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>샘씨엔에스</t>
         </is>
       </c>
       <c r="B99" s="11" t="n">
-        <v>46</v>
+        <v>235</v>
       </c>
       <c r="C99" s="11" t="n">
-        <v>234300916</v>
+        <v>594561536</v>
       </c>
       <c r="D99" s="12" t="inlineStr">
         <is>
-          <t>1.95%→2.35%</t>
+          <t>4.26%→5.06%</t>
         </is>
       </c>
       <c r="E99" s="13" t="inlineStr">
         <is>
-          <t>343→389</t>
+          <t>1,454→1,689</t>
         </is>
       </c>
       <c r="G99" s="14" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>태웅</t>
         </is>
       </c>
       <c r="H99" s="15" t="n">
-        <v>-48</v>
+        <v>-147</v>
       </c>
       <c r="I99" s="15" t="n">
-        <v>-957911656</v>
+        <v>-644411018</v>
       </c>
       <c r="J99" s="16" t="inlineStr">
         <is>
-          <t>6.83%→5.37%</t>
+          <t>1.05%→0.20%</t>
         </is>
       </c>
       <c r="K99" s="13" t="inlineStr">
         <is>
-          <t>275→227</t>
+          <t>186→39</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>코미코</t>
         </is>
       </c>
       <c r="B100" s="11" t="n">
-        <v>30</v>
+        <v>140</v>
       </c>
       <c r="C100" s="11" t="n">
-        <v>245740412</v>
+        <v>569302795</v>
       </c>
       <c r="D100" s="12" t="inlineStr">
         <is>
-          <t>1.90%→1.90%</t>
+          <t>1.28%→1.92%</t>
         </is>
       </c>
       <c r="E100" s="13" t="inlineStr">
         <is>
-          <t>166→196</t>
+          <t>259→399</t>
         </is>
       </c>
       <c r="G100" s="14" t="inlineStr">
         <is>
-          <t>프로텍</t>
+          <t>코세스</t>
         </is>
       </c>
       <c r="H100" s="15" t="n">
-        <v>-41</v>
+        <v>-133</v>
       </c>
       <c r="I100" s="15" t="n">
-        <v>-421090349</v>
+        <v>-847349346</v>
       </c>
       <c r="J100" s="16" t="inlineStr">
         <is>
-          <t>0.94%→0.40%</t>
+          <t>3.83%→4.27%</t>
         </is>
       </c>
       <c r="K100" s="13" t="inlineStr">
         <is>
-          <t>74→33</t>
+          <t>699→566</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" s="10" t="inlineStr">
         <is>
-          <t>리노공업</t>
+          <t>동진쎄미켐</t>
         </is>
       </c>
       <c r="B101" s="11" t="n">
-        <v>21</v>
+        <v>95</v>
       </c>
       <c r="C101" s="11" t="n">
-        <v>225149319</v>
+        <v>637772771</v>
       </c>
       <c r="D101" s="12" t="inlineStr">
         <is>
-          <t>4.47%→4.50%</t>
+          <t>2.23%→2.94%</t>
         </is>
       </c>
       <c r="E101" s="13" t="inlineStr">
         <is>
-          <t>333→354</t>
+          <t>275→370</t>
         </is>
       </c>
       <c r="G101" s="14" t="inlineStr">
         <is>
-          <t>아이쓰리시스템  (편출)</t>
+          <t>네오셈</t>
         </is>
       </c>
       <c r="H101" s="15" t="n">
-        <v>-39</v>
+        <v>-108</v>
       </c>
       <c r="I101" s="15" t="n">
-        <v>-434416944</v>
+        <v>-285870497</v>
       </c>
       <c r="J101" s="16" t="inlineStr">
         <is>
-          <t>0.52%→0.00%</t>
+          <t>2.09%→2.16%</t>
         </is>
       </c>
       <c r="K101" s="13" t="inlineStr">
         <is>
-          <t>39→0</t>
+          <t>797→689</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" s="10" t="inlineStr">
         <is>
+          <t>RFHIC  (신규)</t>
+        </is>
+      </c>
+      <c r="B102" s="11" t="n">
+        <v>88</v>
+      </c>
+      <c r="C102" s="11" t="n">
+        <v>693650951</v>
+      </c>
+      <c r="D102" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.82%</t>
+        </is>
+      </c>
+      <c r="E102" s="13" t="inlineStr">
+        <is>
+          <t>0→88</t>
+        </is>
+      </c>
+      <c r="G102" s="14" t="inlineStr">
+        <is>
+          <t>씨엠티엑스  (편출)</t>
+        </is>
+      </c>
+      <c r="H102" s="15" t="n">
+        <v>-108</v>
+      </c>
+      <c r="I102" s="15" t="n">
+        <v>-1273341143</v>
+      </c>
+      <c r="J102" s="16" t="inlineStr">
+        <is>
+          <t>1.52%→0.00%</t>
+        </is>
+      </c>
+      <c r="K102" s="13" t="inlineStr">
+        <is>
+          <t>108→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="103">
+      <c r="A103" s="10" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="B103" s="11" t="n">
+        <v>85</v>
+      </c>
+      <c r="C103" s="11" t="n">
+        <v>493985823</v>
+      </c>
+      <c r="D103" s="12" t="inlineStr">
+        <is>
+          <t>0.39%→1.02%</t>
+        </is>
+      </c>
+      <c r="E103" s="13" t="inlineStr">
+        <is>
+          <t>63→148</t>
+        </is>
+      </c>
+      <c r="G103" s="14" t="inlineStr">
+        <is>
+          <t>싸이맥스  (편출)</t>
+        </is>
+      </c>
+      <c r="H103" s="15" t="n">
+        <v>-85</v>
+      </c>
+      <c r="I103" s="15" t="n">
+        <v>-298804643</v>
+      </c>
+      <c r="J103" s="16" t="inlineStr">
+        <is>
+          <t>0.36%→0.00%</t>
+        </is>
+      </c>
+      <c r="K103" s="13" t="inlineStr">
+        <is>
+          <t>85→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="104">
+      <c r="A104" s="10" t="inlineStr">
+        <is>
+          <t>이엔에프테크놀로지</t>
+        </is>
+      </c>
+      <c r="B104" s="11" t="n">
+        <v>59</v>
+      </c>
+      <c r="C104" s="11" t="n">
+        <v>405943454</v>
+      </c>
+      <c r="D104" s="12" t="inlineStr">
+        <is>
+          <t>2.89%→3.32%</t>
+        </is>
+      </c>
+      <c r="E104" s="13" t="inlineStr">
+        <is>
+          <t>349→408</t>
+        </is>
+      </c>
+      <c r="G104" s="14" t="inlineStr">
+        <is>
+          <t>원익QnC  (편출)</t>
+        </is>
+      </c>
+      <c r="H104" s="15" t="n">
+        <v>-57</v>
+      </c>
+      <c r="I104" s="15" t="n">
+        <v>-254633159</v>
+      </c>
+      <c r="J104" s="16" t="inlineStr">
+        <is>
+          <t>0.30%→0.00%</t>
+        </is>
+      </c>
+      <c r="K104" s="13" t="inlineStr">
+        <is>
+          <t>57→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="105">
+      <c r="A105" s="10" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="B105" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="C105" s="11" t="n">
+        <v>803536911</v>
+      </c>
+      <c r="D105" s="12" t="inlineStr">
+        <is>
+          <t>1.11%→1.99%</t>
+        </is>
+      </c>
+      <c r="E105" s="13" t="inlineStr">
+        <is>
+          <t>50→96</t>
+        </is>
+      </c>
+      <c r="G105" s="14" t="inlineStr">
+        <is>
+          <t>제주반도체</t>
+        </is>
+      </c>
+      <c r="H105" s="15" t="n">
+        <v>-49</v>
+      </c>
+      <c r="I105" s="15" t="n">
+        <v>-530258209</v>
+      </c>
+      <c r="J105" s="16" t="inlineStr">
+        <is>
+          <t>1.10%→0.49%</t>
+        </is>
+      </c>
+      <c r="K105" s="13" t="inlineStr">
+        <is>
+          <t>87→38</t>
+        </is>
+      </c>
+    </row>
+    <row r="106">
+      <c r="A106" s="10" t="inlineStr">
+        <is>
+          <t>아스플로</t>
+        </is>
+      </c>
+      <c r="B106" s="11" t="n">
+        <v>46</v>
+      </c>
+      <c r="C106" s="11" t="n">
+        <v>234300916</v>
+      </c>
+      <c r="D106" s="12" t="inlineStr">
+        <is>
+          <t>1.95%→2.35%</t>
+        </is>
+      </c>
+      <c r="E106" s="13" t="inlineStr">
+        <is>
+          <t>343→389</t>
+        </is>
+      </c>
+      <c r="G106" s="14" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="H106" s="15" t="n">
+        <v>-48</v>
+      </c>
+      <c r="I106" s="15" t="n">
+        <v>-957911656</v>
+      </c>
+      <c r="J106" s="16" t="inlineStr">
+        <is>
+          <t>6.83%→5.37%</t>
+        </is>
+      </c>
+      <c r="K106" s="13" t="inlineStr">
+        <is>
+          <t>275→227</t>
+        </is>
+      </c>
+    </row>
+    <row r="107">
+      <c r="A107" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B107" s="11" t="n">
+        <v>30</v>
+      </c>
+      <c r="C107" s="11" t="n">
+        <v>245740412</v>
+      </c>
+      <c r="D107" s="12" t="inlineStr">
+        <is>
+          <t>1.90%→1.90%</t>
+        </is>
+      </c>
+      <c r="E107" s="13" t="inlineStr">
+        <is>
+          <t>166→196</t>
+        </is>
+      </c>
+      <c r="G107" s="14" t="inlineStr">
+        <is>
+          <t>프로텍</t>
+        </is>
+      </c>
+      <c r="H107" s="15" t="n">
+        <v>-41</v>
+      </c>
+      <c r="I107" s="15" t="n">
+        <v>-421090349</v>
+      </c>
+      <c r="J107" s="16" t="inlineStr">
+        <is>
+          <t>0.94%→0.40%</t>
+        </is>
+      </c>
+      <c r="K107" s="13" t="inlineStr">
+        <is>
+          <t>74→33</t>
+        </is>
+      </c>
+    </row>
+    <row r="108">
+      <c r="A108" s="10" t="inlineStr">
+        <is>
+          <t>리노공업</t>
+        </is>
+      </c>
+      <c r="B108" s="11" t="n">
+        <v>21</v>
+      </c>
+      <c r="C108" s="11" t="n">
+        <v>225149319</v>
+      </c>
+      <c r="D108" s="12" t="inlineStr">
+        <is>
+          <t>4.47%→4.50%</t>
+        </is>
+      </c>
+      <c r="E108" s="13" t="inlineStr">
+        <is>
+          <t>333→354</t>
+        </is>
+      </c>
+      <c r="G108" s="14" t="inlineStr">
+        <is>
+          <t>아이쓰리시스템  (편출)</t>
+        </is>
+      </c>
+      <c r="H108" s="15" t="n">
+        <v>-39</v>
+      </c>
+      <c r="I108" s="15" t="n">
+        <v>-434416944</v>
+      </c>
+      <c r="J108" s="16" t="inlineStr">
+        <is>
+          <t>0.52%→0.00%</t>
+        </is>
+      </c>
+      <c r="K108" s="13" t="inlineStr">
+        <is>
+          <t>39→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="109">
+      <c r="A109" s="10" t="inlineStr">
+        <is>
           <t>피에스케이</t>
         </is>
       </c>
-      <c r="B102" s="11" t="n">
+      <c r="B109" s="11" t="n">
         <v>16</v>
       </c>
-      <c r="C102" s="11" t="n">
+      <c r="C109" s="11" t="n">
         <v>313158287</v>
       </c>
-      <c r="D102" s="12" t="inlineStr">
+      <c r="D109" s="12" t="inlineStr">
         <is>
           <t>2.68%→2.99%</t>
         </is>
       </c>
-      <c r="E102" s="13" t="inlineStr">
+      <c r="E109" s="13" t="inlineStr">
         <is>
           <t>113→129</t>
         </is>
       </c>
-      <c r="G102" s="14" t="inlineStr">
+      <c r="G109" s="14" t="inlineStr">
         <is>
           <t>파크시스템스</t>
         </is>
       </c>
-      <c r="H102" s="15" t="n">
+      <c r="H109" s="15" t="n">
         <v>-7</v>
       </c>
-      <c r="I102" s="15" t="n">
+      <c r="I109" s="15" t="n">
         <v>-289327396</v>
       </c>
-      <c r="J102" s="16" t="inlineStr">
+      <c r="J109" s="16" t="inlineStr">
         <is>
           <t>2.04%→1.62%</t>
         </is>
       </c>
-      <c r="K102" s="13" t="inlineStr">
+      <c r="K109" s="13" t="inlineStr">
         <is>
           <t>40→33</t>
         </is>
       </c>
     </row>
-    <row r="103">
-      <c r="A103" s="17" t="n"/>
-      <c r="B103" s="17" t="n"/>
-      <c r="C103" s="17" t="n"/>
-      <c r="D103" s="17" t="n"/>
-      <c r="E103" s="17" t="n"/>
-      <c r="G103" s="14" t="inlineStr">
+    <row r="110">
+      <c r="A110" s="17" t="n"/>
+      <c r="B110" s="17" t="n"/>
+      <c r="C110" s="17" t="n"/>
+      <c r="D110" s="17" t="n"/>
+      <c r="E110" s="17" t="n"/>
+      <c r="G110" s="14" t="inlineStr">
         <is>
           <t>티씨케이</t>
         </is>
       </c>
-      <c r="H103" s="15" t="n">
+      <c r="H110" s="15" t="n">
         <v>-6</v>
       </c>
-      <c r="I103" s="15" t="n">
+      <c r="I110" s="15" t="n">
         <v>-217433922</v>
       </c>
-      <c r="J103" s="16" t="inlineStr">
+      <c r="J110" s="16" t="inlineStr">
         <is>
           <t>0.58%→0.30%</t>
         </is>
       </c>
-      <c r="K103" s="13" t="inlineStr">
+      <c r="K110" s="13" t="inlineStr">
         <is>
           <t>13→7</t>
         </is>
       </c>
     </row>
-    <row r="104">
-      <c r="A104" s="17" t="n"/>
-      <c r="B104" s="17" t="n"/>
-      <c r="C104" s="17" t="n"/>
-      <c r="D104" s="17" t="n"/>
-      <c r="E104" s="17" t="n"/>
-      <c r="G104" s="14" t="inlineStr">
+    <row r="111">
+      <c r="A111" s="17" t="n"/>
+      <c r="B111" s="17" t="n"/>
+      <c r="C111" s="17" t="n"/>
+      <c r="D111" s="17" t="n"/>
+      <c r="E111" s="17" t="n"/>
+      <c r="G111" s="14" t="inlineStr">
         <is>
           <t>피에스케이홀딩스</t>
         </is>
       </c>
-      <c r="H104" s="15" t="n">
+      <c r="H111" s="15" t="n">
         <v>-5</v>
       </c>
-      <c r="I104" s="15" t="n">
+      <c r="I111" s="15" t="n">
         <v>-140697449</v>
       </c>
-      <c r="J104" s="16" t="inlineStr">
+      <c r="J111" s="16" t="inlineStr">
         <is>
           <t>2.55%→2.13%</t>
         </is>
       </c>
-      <c r="K104" s="13" t="inlineStr">
+      <c r="K111" s="13" t="inlineStr">
         <is>
           <t>69→64</t>
         </is>
       </c>
     </row>
-    <row r="105">
-      <c r="A105" s="17" t="n"/>
-      <c r="B105" s="17" t="n"/>
-      <c r="C105" s="17" t="n"/>
-      <c r="D105" s="17" t="n"/>
-      <c r="E105" s="17" t="n"/>
-      <c r="G105" s="14" t="inlineStr">
+    <row r="112">
+      <c r="A112" s="17" t="n"/>
+      <c r="B112" s="17" t="n"/>
+      <c r="C112" s="17" t="n"/>
+      <c r="D112" s="17" t="n"/>
+      <c r="E112" s="17" t="n"/>
+      <c r="G112" s="14" t="inlineStr">
         <is>
           <t>이오테크닉스</t>
         </is>
       </c>
-      <c r="H105" s="15" t="n">
+      <c r="H112" s="15" t="n">
         <v>-4</v>
       </c>
-      <c r="I105" s="15" t="n">
+      <c r="I112" s="15" t="n">
         <v>-273879902</v>
       </c>
-      <c r="J105" s="16" t="inlineStr">
+      <c r="J112" s="16" t="inlineStr">
         <is>
           <t>4.48%→3.97%</t>
         </is>
       </c>
-      <c r="K105" s="13" t="inlineStr">
+      <c r="K112" s="13" t="inlineStr">
         <is>
           <t>53→49</t>
         </is>
       </c>
     </row>
-    <row r="106">
-      <c r="A106" s="17" t="n"/>
-      <c r="B106" s="17" t="n"/>
-      <c r="C106" s="17" t="n"/>
-      <c r="D106" s="17" t="n"/>
-      <c r="E106" s="17" t="n"/>
-      <c r="G106" s="14" t="inlineStr">
+    <row r="113">
+      <c r="A113" s="17" t="n"/>
+      <c r="B113" s="17" t="n"/>
+      <c r="C113" s="17" t="n"/>
+      <c r="D113" s="17" t="n"/>
+      <c r="E113" s="17" t="n"/>
+      <c r="G113" s="14" t="inlineStr">
         <is>
           <t>티에스이</t>
         </is>
       </c>
-      <c r="H106" s="15" t="n">
+      <c r="H113" s="15" t="n">
         <v>-4</v>
       </c>
-      <c r="I106" s="15" t="n">
+      <c r="I113" s="15" t="n">
         <v>-170005939</v>
       </c>
-      <c r="J106" s="16" t="inlineStr">
+      <c r="J113" s="16" t="inlineStr">
         <is>
           <t>2.50%→2.11%</t>
         </is>
       </c>
-      <c r="K106" s="13" t="inlineStr">
+      <c r="K113" s="13" t="inlineStr">
         <is>
           <t>46→42</t>
         </is>
       </c>
     </row>
-    <row r="108" ht="19" customHeight="1">
-      <c r="A108" s="18" t="inlineStr">
-        <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B108" s="19" t="n"/>
-      <c r="C108" s="19" t="n"/>
-      <c r="D108" s="19" t="n"/>
-      <c r="E108" s="19" t="n"/>
-      <c r="F108" s="19" t="n"/>
-      <c r="G108" s="19" t="n"/>
-      <c r="H108" s="19" t="n"/>
-      <c r="I108" s="19" t="n"/>
-      <c r="J108" s="19" t="n"/>
-      <c r="K108" s="19" t="n"/>
-    </row>
-    <row r="110" ht="19" customHeight="1">
-      <c r="A110" s="18" t="inlineStr">
-        <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      ⏳ 대기 — 당일 PDF 미게시/지연 (게시되면 자동 반영)</t>
-        </is>
-      </c>
-      <c r="B110" s="19" t="n"/>
-      <c r="C110" s="19" t="n"/>
-      <c r="D110" s="19" t="n"/>
-      <c r="E110" s="19" t="n"/>
-      <c r="F110" s="19" t="n"/>
-      <c r="G110" s="19" t="n"/>
-      <c r="H110" s="19" t="n"/>
-      <c r="I110" s="19" t="n"/>
-      <c r="J110" s="19" t="n"/>
-      <c r="K110" s="19" t="n"/>
+    <row r="115" ht="19" customHeight="1">
+      <c r="A115" s="3" t="inlineStr">
+        <is>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 303억   ·   현금 7억(2.2%)      오늘 2026-10-23  vs  5일전 2026-10-16      매수 15종목  /  매도 24종목</t>
+        </is>
+      </c>
+      <c r="B115" s="4" t="n"/>
+      <c r="C115" s="4" t="n"/>
+      <c r="D115" s="4" t="n"/>
+      <c r="E115" s="4" t="n"/>
+      <c r="F115" s="4" t="n"/>
+      <c r="G115" s="4" t="n"/>
+      <c r="H115" s="4" t="n"/>
+      <c r="I115" s="4" t="n"/>
+      <c r="J115" s="4" t="n"/>
+      <c r="K115" s="4" t="n"/>
+    </row>
+    <row r="116">
+      <c r="A116" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B116" s="6" t="n"/>
+      <c r="C116" s="6" t="n"/>
+      <c r="D116" s="6" t="n"/>
+      <c r="E116" s="6" t="n"/>
+      <c r="G116" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H116" s="8" t="n"/>
+      <c r="I116" s="8" t="n"/>
+      <c r="J116" s="8" t="n"/>
+      <c r="K116" s="8" t="n"/>
+    </row>
+    <row r="117">
+      <c r="A117" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B117" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C117" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D117" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E117" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G117" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H117" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I117" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J117" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K117" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="118">
+      <c r="A118" s="10" t="inlineStr">
+        <is>
+          <t>파인엠텍  (신규)</t>
+        </is>
+      </c>
+      <c r="B118" s="11" t="n">
+        <v>77</v>
+      </c>
+      <c r="C118" s="11" t="n">
+        <v>333963630</v>
+      </c>
+      <c r="D118" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.13%</t>
+        </is>
+      </c>
+      <c r="E118" s="13" t="inlineStr">
+        <is>
+          <t>0→77</t>
+        </is>
+      </c>
+      <c r="G118" s="14" t="inlineStr">
+        <is>
+          <t>동국산업</t>
+        </is>
+      </c>
+      <c r="H118" s="15" t="n">
+        <v>-135</v>
+      </c>
+      <c r="I118" s="15" t="n">
+        <v>-232528725</v>
+      </c>
+      <c r="J118" s="16" t="inlineStr">
+        <is>
+          <t>1.81%→0.98%</t>
+        </is>
+      </c>
+      <c r="K118" s="13" t="inlineStr">
+        <is>
+          <t>303→168</t>
+        </is>
+      </c>
+    </row>
+    <row r="119">
+      <c r="A119" s="10" t="inlineStr">
+        <is>
+          <t>코세스</t>
+        </is>
+      </c>
+      <c r="B119" s="11" t="n">
+        <v>66</v>
+      </c>
+      <c r="C119" s="11" t="n">
+        <v>1080179100</v>
+      </c>
+      <c r="D119" s="12" t="inlineStr">
+        <is>
+          <t>2.66%→7.23%</t>
+        </is>
+      </c>
+      <c r="E119" s="13" t="inlineStr">
+        <is>
+          <t>65→131</t>
+        </is>
+      </c>
+      <c r="G119" s="14" t="inlineStr">
+        <is>
+          <t>LS머트리얼즈  (편출)</t>
+        </is>
+      </c>
+      <c r="H119" s="15" t="n">
+        <v>-73</v>
+      </c>
+      <c r="I119" s="15" t="n">
+        <v>-438124830</v>
+      </c>
+      <c r="J119" s="16" t="inlineStr">
+        <is>
+          <t>1.53%→0.00%</t>
+        </is>
+      </c>
+      <c r="K119" s="13" t="inlineStr">
+        <is>
+          <t>73→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="120">
+      <c r="A120" s="10" t="inlineStr">
+        <is>
+          <t>샘씨엔에스</t>
+        </is>
+      </c>
+      <c r="B120" s="11" t="n">
+        <v>65</v>
+      </c>
+      <c r="C120" s="11" t="n">
+        <v>422457750</v>
+      </c>
+      <c r="D120" s="12" t="inlineStr">
+        <is>
+          <t>1.67%→3.09%</t>
+        </is>
+      </c>
+      <c r="E120" s="13" t="inlineStr">
+        <is>
+          <t>76→141</t>
+        </is>
+      </c>
+      <c r="G120" s="14" t="inlineStr">
+        <is>
+          <t>더블유씨피  (편출)</t>
+        </is>
+      </c>
+      <c r="H120" s="15" t="n">
+        <v>-67</v>
+      </c>
+      <c r="I120" s="15" t="n">
+        <v>-287142570</v>
+      </c>
+      <c r="J120" s="16" t="inlineStr">
+        <is>
+          <t>1.00%→0.00%</t>
+        </is>
+      </c>
+      <c r="K120" s="13" t="inlineStr">
+        <is>
+          <t>67→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="121">
+      <c r="A121" s="10" t="inlineStr">
+        <is>
+          <t>서진시스템</t>
+        </is>
+      </c>
+      <c r="B121" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C121" s="11" t="n">
+        <v>291291000</v>
+      </c>
+      <c r="D121" s="12" t="inlineStr">
+        <is>
+          <t>3.63%→4.37%</t>
+        </is>
+      </c>
+      <c r="E121" s="13" t="inlineStr">
+        <is>
+          <t>69→89</t>
+        </is>
+      </c>
+      <c r="G121" s="14" t="inlineStr">
+        <is>
+          <t>에이팩트</t>
+        </is>
+      </c>
+      <c r="H121" s="15" t="n">
+        <v>-62</v>
+      </c>
+      <c r="I121" s="15" t="n">
+        <v>-229274760</v>
+      </c>
+      <c r="J121" s="16" t="inlineStr">
+        <is>
+          <t>3.32%→2.21%</t>
+        </is>
+      </c>
+      <c r="K121" s="13" t="inlineStr">
+        <is>
+          <t>239→177</t>
+        </is>
+      </c>
+    </row>
+    <row r="122">
+      <c r="A122" s="10" t="inlineStr">
+        <is>
+          <t>지투지바이오</t>
+        </is>
+      </c>
+      <c r="B122" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C122" s="11" t="n">
+        <v>353496000</v>
+      </c>
+      <c r="D122" s="12" t="inlineStr">
+        <is>
+          <t>0.41%→1.73%</t>
+        </is>
+      </c>
+      <c r="E122" s="13" t="inlineStr">
+        <is>
+          <t>9→29</t>
+        </is>
+      </c>
+      <c r="G122" s="14" t="inlineStr">
+        <is>
+          <t>피엠티  (편출)</t>
+        </is>
+      </c>
+      <c r="H122" s="15" t="n">
+        <v>-53</v>
+      </c>
+      <c r="I122" s="15" t="n">
+        <v>-74804730</v>
+      </c>
+      <c r="J122" s="16" t="inlineStr">
+        <is>
+          <t>0.26%→0.00%</t>
+        </is>
+      </c>
+      <c r="K122" s="13" t="inlineStr">
+        <is>
+          <t>53→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="123">
+      <c r="A123" s="10" t="inlineStr">
+        <is>
+          <t>프로티나  (신규)</t>
+        </is>
+      </c>
+      <c r="B123" s="11" t="n">
+        <v>20</v>
+      </c>
+      <c r="C123" s="11" t="n">
+        <v>366795000</v>
+      </c>
+      <c r="D123" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.24%</t>
+        </is>
+      </c>
+      <c r="E123" s="13" t="inlineStr">
+        <is>
+          <t>0→20</t>
+        </is>
+      </c>
+      <c r="G123" s="14" t="inlineStr">
+        <is>
+          <t>덕산하이메탈</t>
+        </is>
+      </c>
+      <c r="H123" s="15" t="n">
+        <v>-49</v>
+      </c>
+      <c r="I123" s="15" t="n">
+        <v>-232912680</v>
+      </c>
+      <c r="J123" s="16" t="inlineStr">
+        <is>
+          <t>1.47%→0.64%</t>
+        </is>
+      </c>
+      <c r="K123" s="13" t="inlineStr">
+        <is>
+          <t>89→40</t>
+        </is>
+      </c>
+    </row>
+    <row r="124">
+      <c r="A124" s="10" t="inlineStr">
+        <is>
+          <t>태성</t>
+        </is>
+      </c>
+      <c r="B124" s="11" t="n">
+        <v>13</v>
+      </c>
+      <c r="C124" s="11" t="n">
+        <v>288888600</v>
+      </c>
+      <c r="D124" s="12" t="inlineStr">
+        <is>
+          <t>1.04%→1.95%</t>
+        </is>
+      </c>
+      <c r="E124" s="13" t="inlineStr">
+        <is>
+          <t>13→26</t>
+        </is>
+      </c>
+      <c r="G124" s="14" t="inlineStr">
+        <is>
+          <t>HT로보틱스  (편출)</t>
+        </is>
+      </c>
+      <c r="H124" s="15" t="n">
+        <v>-48</v>
+      </c>
+      <c r="I124" s="15" t="n">
+        <v>-147232800</v>
+      </c>
+      <c r="J124" s="16" t="inlineStr">
+        <is>
+          <t>0.51%→0.00%</t>
+        </is>
+      </c>
+      <c r="K124" s="13" t="inlineStr">
+        <is>
+          <t>48→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="125">
+      <c r="A125" s="10" t="inlineStr">
+        <is>
+          <t>RF머트리얼즈</t>
+        </is>
+      </c>
+      <c r="B125" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C125" s="11" t="n">
+        <v>201737250</v>
+      </c>
+      <c r="D125" s="12" t="inlineStr">
+        <is>
+          <t>0.37%→1.05%</t>
+        </is>
+      </c>
+      <c r="E125" s="13" t="inlineStr">
+        <is>
+          <t>6→17</t>
+        </is>
+      </c>
+      <c r="G125" s="14" t="inlineStr">
+        <is>
+          <t>글로벌텍스프리</t>
+        </is>
+      </c>
+      <c r="H125" s="15" t="n">
+        <v>-46</v>
+      </c>
+      <c r="I125" s="15" t="n">
+        <v>-108537000</v>
+      </c>
+      <c r="J125" s="16" t="inlineStr">
+        <is>
+          <t>1.16%→0.68%</t>
+        </is>
+      </c>
+      <c r="K125" s="13" t="inlineStr">
+        <is>
+          <t>132→86</t>
+        </is>
+      </c>
+    </row>
+    <row r="126">
+      <c r="A126" s="10" t="inlineStr">
+        <is>
+          <t>선익시스템  (신규)</t>
+        </is>
+      </c>
+      <c r="B126" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C126" s="11" t="n">
+        <v>313513200</v>
+      </c>
+      <c r="D126" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→1.06%</t>
+        </is>
+      </c>
+      <c r="E126" s="13" t="inlineStr">
+        <is>
+          <t>0→9</t>
+        </is>
+      </c>
+      <c r="G126" s="14" t="inlineStr">
+        <is>
+          <t>피노</t>
+        </is>
+      </c>
+      <c r="H126" s="15" t="n">
+        <v>-40</v>
+      </c>
+      <c r="I126" s="15" t="n">
+        <v>-125782800</v>
+      </c>
+      <c r="J126" s="16" t="inlineStr">
+        <is>
+          <t>4.12%→2.85%</t>
+        </is>
+      </c>
+      <c r="K126" s="13" t="inlineStr">
+        <is>
+          <t>309→269</t>
+        </is>
+      </c>
+    </row>
+    <row r="127">
+      <c r="A127" s="10" t="inlineStr">
+        <is>
+          <t>알지노믹스</t>
+        </is>
+      </c>
+      <c r="B127" s="11" t="n">
+        <v>9</v>
+      </c>
+      <c r="C127" s="11" t="n">
+        <v>95366700</v>
+      </c>
+      <c r="D127" s="12" t="inlineStr">
+        <is>
+          <t>0.65%→1.07%</t>
+        </is>
+      </c>
+      <c r="E127" s="13" t="inlineStr">
+        <is>
+          <t>21→30</t>
+        </is>
+      </c>
+      <c r="G127" s="14" t="inlineStr">
+        <is>
+          <t>덕산테코피아</t>
+        </is>
+      </c>
+      <c r="H127" s="15" t="n">
+        <v>-28</v>
+      </c>
+      <c r="I127" s="15" t="n">
+        <v>-122882760</v>
+      </c>
+      <c r="J127" s="16" t="inlineStr">
+        <is>
+          <t>0.66%→0.19%</t>
+        </is>
+      </c>
+      <c r="K127" s="13" t="inlineStr">
+        <is>
+          <t>41→13</t>
+        </is>
+      </c>
+    </row>
+    <row r="128">
+      <c r="A128" s="10" t="inlineStr">
+        <is>
+          <t>지엔씨에너지</t>
+        </is>
+      </c>
+      <c r="B128" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C128" s="11" t="n">
+        <v>127327200</v>
+      </c>
+      <c r="D128" s="12" t="inlineStr">
+        <is>
+          <t>0.53%→0.98%</t>
+        </is>
+      </c>
+      <c r="E128" s="13" t="inlineStr">
+        <is>
+          <t>9→16</t>
+        </is>
+      </c>
+      <c r="G128" s="14" t="inlineStr">
+        <is>
+          <t>성호전자  (편출)</t>
+        </is>
+      </c>
+      <c r="H128" s="15" t="n">
+        <v>-27</v>
+      </c>
+      <c r="I128" s="15" t="n">
+        <v>-315057600</v>
+      </c>
+      <c r="J128" s="16" t="inlineStr">
+        <is>
+          <t>1.10%→0.00%</t>
+        </is>
+      </c>
+      <c r="K128" s="13" t="inlineStr">
+        <is>
+          <t>27→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="129">
+      <c r="A129" s="10" t="inlineStr">
+        <is>
+          <t>심텍</t>
+        </is>
+      </c>
+      <c r="B129" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C129" s="11" t="n">
+        <v>358858500</v>
+      </c>
+      <c r="D129" s="12" t="inlineStr">
+        <is>
+          <t>5.01%→5.87%</t>
+        </is>
+      </c>
+      <c r="E129" s="13" t="inlineStr">
+        <is>
+          <t>27→34</t>
+        </is>
+      </c>
+      <c r="G129" s="14" t="inlineStr">
+        <is>
+          <t>엔알비  (편출)</t>
+        </is>
+      </c>
+      <c r="H129" s="15" t="n">
+        <v>-23</v>
+      </c>
+      <c r="I129" s="15" t="n">
+        <v>-75581220</v>
+      </c>
+      <c r="J129" s="16" t="inlineStr">
+        <is>
+          <t>0.26%→0.00%</t>
+        </is>
+      </c>
+      <c r="K129" s="13" t="inlineStr">
+        <is>
+          <t>23→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="130">
+      <c r="A130" s="10" t="inlineStr">
+        <is>
+          <t>올릭스</t>
+        </is>
+      </c>
+      <c r="B130" s="11" t="n">
+        <v>7</v>
+      </c>
+      <c r="C130" s="11" t="n">
+        <v>317116800</v>
+      </c>
+      <c r="D130" s="12" t="inlineStr">
+        <is>
+          <t>2.35%→3.82%</t>
+        </is>
+      </c>
+      <c r="E130" s="13" t="inlineStr">
+        <is>
+          <t>18→25</t>
+        </is>
+      </c>
+      <c r="G130" s="14" t="inlineStr">
+        <is>
+          <t>네오티스</t>
+        </is>
+      </c>
+      <c r="H130" s="15" t="n">
+        <v>-21</v>
+      </c>
+      <c r="I130" s="15" t="n">
+        <v>-175855680</v>
+      </c>
+      <c r="J130" s="16" t="inlineStr">
+        <is>
+          <t>1.18%→0.65%</t>
+        </is>
+      </c>
+      <c r="K130" s="13" t="inlineStr">
+        <is>
+          <t>44→23</t>
+        </is>
+      </c>
+    </row>
+    <row r="131">
+      <c r="A131" s="10" t="inlineStr">
+        <is>
+          <t>HPSP</t>
+        </is>
+      </c>
+      <c r="B131" s="11" t="n">
+        <v>3</v>
+      </c>
+      <c r="C131" s="11" t="n">
+        <v>62290800</v>
+      </c>
+      <c r="D131" s="12" t="inlineStr">
+        <is>
+          <t>0.74%→0.91%</t>
+        </is>
+      </c>
+      <c r="E131" s="13" t="inlineStr">
+        <is>
+          <t>10→13</t>
+        </is>
+      </c>
+      <c r="G131" s="14" t="inlineStr">
+        <is>
+          <t>큐리언트  (편출)</t>
+        </is>
+      </c>
+      <c r="H131" s="15" t="n">
+        <v>-20</v>
+      </c>
+      <c r="I131" s="15" t="n">
+        <v>-178464000</v>
+      </c>
+      <c r="J131" s="16" t="inlineStr">
+        <is>
+          <t>0.62%→0.00%</t>
+        </is>
+      </c>
+      <c r="K131" s="13" t="inlineStr">
+        <is>
+          <t>20→0</t>
+        </is>
+      </c>
+    </row>
+    <row r="132">
+      <c r="A132" s="10" t="inlineStr">
+        <is>
+          <t>이오테크닉스  (신규)</t>
+        </is>
+      </c>
+      <c r="B132" s="11" t="n">
+        <v>1</v>
+      </c>
+      <c r="C132" s="11" t="n">
+        <v>175890000</v>
+      </c>
+      <c r="D132" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.59%</t>
+        </is>
+      </c>
+      <c r="E132" s="13" t="inlineStr">
+        <is>
+          <t>0→1</t>
+        </is>
+      </c>
+      <c r="G132" s="14" t="inlineStr">
+        <is>
+          <t>HLB이노베이션</t>
+        </is>
+      </c>
+      <c r="H132" s="15" t="n">
+        <v>-12</v>
+      </c>
+      <c r="I132" s="15" t="n">
+        <v>-81750240</v>
+      </c>
+      <c r="J132" s="16" t="inlineStr">
+        <is>
+          <t>1.00%→0.64%</t>
+        </is>
+      </c>
+      <c r="K132" s="13" t="inlineStr">
+        <is>
+          <t>40→28</t>
+        </is>
+      </c>
+    </row>
+    <row r="133">
+      <c r="A133" s="17" t="n"/>
+      <c r="B133" s="17" t="n"/>
+      <c r="C133" s="17" t="n"/>
+      <c r="D133" s="17" t="n"/>
+      <c r="E133" s="17" t="n"/>
+      <c r="G133" s="14" t="inlineStr">
+        <is>
+          <t>네패스</t>
+        </is>
+      </c>
+      <c r="H133" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I133" s="15" t="n">
+        <v>-110660550</v>
+      </c>
+      <c r="J133" s="16" t="inlineStr">
+        <is>
+          <t>1.01%→0.54%</t>
+        </is>
+      </c>
+      <c r="K133" s="13" t="inlineStr">
+        <is>
+          <t>27→16</t>
+        </is>
+      </c>
+    </row>
+    <row r="134">
+      <c r="A134" s="17" t="n"/>
+      <c r="B134" s="17" t="n"/>
+      <c r="C134" s="17" t="n"/>
+      <c r="D134" s="17" t="n"/>
+      <c r="E134" s="17" t="n"/>
+      <c r="G134" s="14" t="inlineStr">
+        <is>
+          <t>오킨스전자</t>
+        </is>
+      </c>
+      <c r="H134" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I134" s="15" t="n">
+        <v>-113256000</v>
+      </c>
+      <c r="J134" s="16" t="inlineStr">
+        <is>
+          <t>1.26%→0.80%</t>
+        </is>
+      </c>
+      <c r="K134" s="13" t="inlineStr">
+        <is>
+          <t>34→23</t>
+        </is>
+      </c>
+    </row>
+    <row r="135">
+      <c r="A135" s="17" t="n"/>
+      <c r="B135" s="17" t="n"/>
+      <c r="C135" s="17" t="n"/>
+      <c r="D135" s="17" t="n"/>
+      <c r="E135" s="17" t="n"/>
+      <c r="G135" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이</t>
+        </is>
+      </c>
+      <c r="H135" s="15" t="n">
+        <v>-11</v>
+      </c>
+      <c r="I135" s="15" t="n">
+        <v>-553066800</v>
+      </c>
+      <c r="J135" s="16" t="inlineStr">
+        <is>
+          <t>3.01%→1.02%</t>
+        </is>
+      </c>
+      <c r="K135" s="13" t="inlineStr">
+        <is>
+          <t>17→6</t>
+        </is>
+      </c>
+    </row>
+    <row r="136">
+      <c r="A136" s="17" t="n"/>
+      <c r="B136" s="17" t="n"/>
+      <c r="C136" s="17" t="n"/>
+      <c r="D136" s="17" t="n"/>
+      <c r="E136" s="17" t="n"/>
+      <c r="G136" s="14" t="inlineStr">
+        <is>
+          <t>오이솔루션</t>
+        </is>
+      </c>
+      <c r="H136" s="15" t="n">
+        <v>-7</v>
+      </c>
+      <c r="I136" s="15" t="n">
+        <v>-77177100</v>
+      </c>
+      <c r="J136" s="16" t="inlineStr">
+        <is>
+          <t>1.03%→0.78%</t>
+        </is>
+      </c>
+      <c r="K136" s="13" t="inlineStr">
+        <is>
+          <t>28→21</t>
+        </is>
+      </c>
+    </row>
+    <row r="137">
+      <c r="A137" s="17" t="n"/>
+      <c r="B137" s="17" t="n"/>
+      <c r="C137" s="17" t="n"/>
+      <c r="D137" s="17" t="n"/>
+      <c r="E137" s="17" t="n"/>
+      <c r="G137" s="14" t="inlineStr">
+        <is>
+          <t>인텔리안테크</t>
+        </is>
+      </c>
+      <c r="H137" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I137" s="15" t="n">
+        <v>-117331500</v>
+      </c>
+      <c r="J137" s="16" t="inlineStr">
+        <is>
+          <t>0.81%→0.40%</t>
+        </is>
+      </c>
+      <c r="K137" s="13" t="inlineStr">
+        <is>
+          <t>10→5</t>
+        </is>
+      </c>
+    </row>
+    <row r="138">
+      <c r="A138" s="17" t="n"/>
+      <c r="B138" s="17" t="n"/>
+      <c r="C138" s="17" t="n"/>
+      <c r="D138" s="17" t="n"/>
+      <c r="E138" s="17" t="n"/>
+      <c r="G138" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H138" s="15" t="n">
+        <v>-5</v>
+      </c>
+      <c r="I138" s="15" t="n">
+        <v>-233376000</v>
+      </c>
+      <c r="J138" s="16" t="inlineStr">
+        <is>
+          <t>2.03%→0.94%</t>
+        </is>
+      </c>
+      <c r="K138" s="13" t="inlineStr">
+        <is>
+          <t>11→6</t>
+        </is>
+      </c>
+    </row>
+    <row r="139">
+      <c r="A139" s="17" t="n"/>
+      <c r="B139" s="17" t="n"/>
+      <c r="C139" s="17" t="n"/>
+      <c r="D139" s="17" t="n"/>
+      <c r="E139" s="17" t="n"/>
+      <c r="G139" s="14" t="inlineStr">
+        <is>
+          <t>펌텍코리아</t>
+        </is>
+      </c>
+      <c r="H139" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I139" s="15" t="n">
+        <v>-119776800</v>
+      </c>
+      <c r="J139" s="16" t="inlineStr">
+        <is>
+          <t>3.60%→3.23%</t>
+        </is>
+      </c>
+      <c r="K139" s="13" t="inlineStr">
+        <is>
+          <t>36→32</t>
+        </is>
+      </c>
+    </row>
+    <row r="140">
+      <c r="A140" s="17" t="n"/>
+      <c r="B140" s="17" t="n"/>
+      <c r="C140" s="17" t="n"/>
+      <c r="D140" s="17" t="n"/>
+      <c r="E140" s="17" t="n"/>
+      <c r="G140" s="14" t="inlineStr">
+        <is>
+          <t>기가비스</t>
+        </is>
+      </c>
+      <c r="H140" s="15" t="n">
+        <v>-4</v>
+      </c>
+      <c r="I140" s="15" t="n">
+        <v>-179493600</v>
+      </c>
+      <c r="J140" s="16" t="inlineStr">
+        <is>
+          <t>1.16%→0.45%</t>
+        </is>
+      </c>
+      <c r="K140" s="13" t="inlineStr">
+        <is>
+          <t>7→3</t>
+        </is>
+      </c>
+    </row>
+    <row r="141">
+      <c r="A141" s="17" t="n"/>
+      <c r="B141" s="17" t="n"/>
+      <c r="C141" s="17" t="n"/>
+      <c r="D141" s="17" t="n"/>
+      <c r="E141" s="17" t="n"/>
+      <c r="G141" s="14" t="inlineStr">
+        <is>
+          <t>한라IMS</t>
+        </is>
+      </c>
+      <c r="H141" s="15" t="n">
+        <v>-3</v>
+      </c>
+      <c r="I141" s="15" t="n">
+        <v>-18815940</v>
+      </c>
+      <c r="J141" s="16" t="inlineStr">
+        <is>
+          <t>0.40%→0.30%</t>
+        </is>
+      </c>
+      <c r="K141" s="13" t="inlineStr">
+        <is>
+          <t>17→14</t>
+        </is>
+      </c>
+    </row>
+    <row r="143" ht="19" customHeight="1">
+      <c r="A143" s="3" t="inlineStr">
+        <is>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 56억   ·   현금 1억(1.7%)      오늘 2026-10-23  vs  5일전 2026-10-16      매수 4종목  /  매도 3종목</t>
+        </is>
+      </c>
+      <c r="B143" s="4" t="n"/>
+      <c r="C143" s="4" t="n"/>
+      <c r="D143" s="4" t="n"/>
+      <c r="E143" s="4" t="n"/>
+      <c r="F143" s="4" t="n"/>
+      <c r="G143" s="4" t="n"/>
+      <c r="H143" s="4" t="n"/>
+      <c r="I143" s="4" t="n"/>
+      <c r="J143" s="4" t="n"/>
+      <c r="K143" s="4" t="n"/>
+    </row>
+    <row r="144">
+      <c r="A144" s="5" t="inlineStr">
+        <is>
+          <t>🔴 매수 (확대·신규편입)</t>
+        </is>
+      </c>
+      <c r="B144" s="6" t="n"/>
+      <c r="C144" s="6" t="n"/>
+      <c r="D144" s="6" t="n"/>
+      <c r="E144" s="6" t="n"/>
+      <c r="G144" s="7" t="inlineStr">
+        <is>
+          <t>🔵 매도 (축소·편출)</t>
+        </is>
+      </c>
+      <c r="H144" s="8" t="n"/>
+      <c r="I144" s="8" t="n"/>
+      <c r="J144" s="8" t="n"/>
+      <c r="K144" s="8" t="n"/>
+    </row>
+    <row r="145">
+      <c r="A145" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="B145" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="C145" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="D145" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="E145" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+      <c r="G145" s="9" t="inlineStr">
+        <is>
+          <t>종목명</t>
+        </is>
+      </c>
+      <c r="H145" s="9" t="inlineStr">
+        <is>
+          <t>변화(1CU주)</t>
+        </is>
+      </c>
+      <c r="I145" s="9" t="inlineStr">
+        <is>
+          <t>전체매매금액(원)</t>
+        </is>
+      </c>
+      <c r="J145" s="9" t="inlineStr">
+        <is>
+          <t>보유비중(전→당)</t>
+        </is>
+      </c>
+      <c r="K145" s="9" t="inlineStr">
+        <is>
+          <t>전일→당일</t>
+        </is>
+      </c>
+    </row>
+    <row r="146">
+      <c r="A146" s="10" t="inlineStr">
+        <is>
+          <t>큐리언트  (신규)</t>
+        </is>
+      </c>
+      <c r="B146" s="11" t="n">
+        <v>176</v>
+      </c>
+      <c r="C146" s="11" t="n">
+        <v>28441600</v>
+      </c>
+      <c r="D146" s="12" t="inlineStr">
+        <is>
+          <t>0.00%→0.51%</t>
+        </is>
+      </c>
+      <c r="E146" s="13" t="inlineStr">
+        <is>
+          <t>0→176</t>
+        </is>
+      </c>
+      <c r="G146" s="14" t="inlineStr">
+        <is>
+          <t>엘티씨</t>
+        </is>
+      </c>
+      <c r="H146" s="15" t="n">
+        <v>-98</v>
+      </c>
+      <c r="I146" s="15" t="n">
+        <v>-27283200</v>
+      </c>
+      <c r="J146" s="16" t="inlineStr">
+        <is>
+          <t>3.44%→2.93%</t>
+        </is>
+      </c>
+      <c r="K146" s="13" t="inlineStr">
+        <is>
+          <t>683→585</t>
+        </is>
+      </c>
+    </row>
+    <row r="147">
+      <c r="A147" s="10" t="inlineStr">
+        <is>
+          <t>파두</t>
+        </is>
+      </c>
+      <c r="B147" s="11" t="n">
+        <v>56</v>
+      </c>
+      <c r="C147" s="11" t="n">
+        <v>21974400</v>
+      </c>
+      <c r="D147" s="12" t="inlineStr">
+        <is>
+          <t>3.18%→3.57%</t>
+        </is>
+      </c>
+      <c r="E147" s="13" t="inlineStr">
+        <is>
+          <t>449→505</t>
+        </is>
+      </c>
+      <c r="G147" s="14" t="inlineStr">
+        <is>
+          <t>테스</t>
+        </is>
+      </c>
+      <c r="H147" s="15" t="n">
+        <v>-28</v>
+      </c>
+      <c r="I147" s="15" t="n">
+        <v>-24371200</v>
+      </c>
+      <c r="J147" s="16" t="inlineStr">
+        <is>
+          <t>4.36%→3.90%</t>
+        </is>
+      </c>
+      <c r="K147" s="13" t="inlineStr">
+        <is>
+          <t>277→249</t>
+        </is>
+      </c>
+    </row>
+    <row r="148">
+      <c r="A148" s="10" t="inlineStr">
+        <is>
+          <t>대주전자재료</t>
+        </is>
+      </c>
+      <c r="B148" s="11" t="n">
+        <v>12</v>
+      </c>
+      <c r="C148" s="11" t="n">
+        <v>9792000</v>
+      </c>
+      <c r="D148" s="12" t="inlineStr">
+        <is>
+          <t>2.61%→2.78%</t>
+        </is>
+      </c>
+      <c r="E148" s="13" t="inlineStr">
+        <is>
+          <t>177→189</t>
+        </is>
+      </c>
+      <c r="G148" s="14" t="inlineStr">
+        <is>
+          <t>피에스케이홀딩스</t>
+        </is>
+      </c>
+      <c r="H148" s="15" t="n">
+        <v>-19</v>
+      </c>
+      <c r="I148" s="15" t="n">
+        <v>-25612000</v>
+      </c>
+      <c r="J148" s="16" t="inlineStr">
+        <is>
+          <t>4.92%→4.44%</t>
+        </is>
+      </c>
+      <c r="K148" s="13" t="inlineStr">
+        <is>
+          <t>202→183</t>
+        </is>
+      </c>
+    </row>
+    <row r="149">
+      <c r="A149" s="10" t="inlineStr">
+        <is>
+          <t>이오테크닉스</t>
+        </is>
+      </c>
+      <c r="B149" s="11" t="n">
+        <v>11</v>
+      </c>
+      <c r="C149" s="11" t="n">
+        <v>36080000</v>
+      </c>
+      <c r="D149" s="12" t="inlineStr">
+        <is>
+          <t>5.99%→6.62%</t>
+        </is>
+      </c>
+      <c r="E149" s="13" t="inlineStr">
+        <is>
+          <t>101→112</t>
+        </is>
+      </c>
+      <c r="G149" s="17" t="n"/>
+      <c r="H149" s="17" t="n"/>
+      <c r="I149" s="17" t="n"/>
+      <c r="J149" s="17" t="n"/>
+      <c r="K149" s="17" t="n"/>
     </row>
   </sheetData>
-  <mergeCells count="24">
+  <mergeCells count="30">
     <mergeCell ref="A34:E34"/>
+    <mergeCell ref="A143:K143"/>
     <mergeCell ref="A82:K82"/>
     <mergeCell ref="A24:K24"/>
+    <mergeCell ref="A94:E94"/>
     <mergeCell ref="A60:K60"/>
     <mergeCell ref="A61:E61"/>
     <mergeCell ref="G61:K61"/>
     <mergeCell ref="A1:K1"/>
     <mergeCell ref="A70:E70"/>
     <mergeCell ref="G70:K70"/>
-    <mergeCell ref="A110:K110"/>
     <mergeCell ref="A69:K69"/>
-    <mergeCell ref="A87:E87"/>
+    <mergeCell ref="G116:K116"/>
     <mergeCell ref="A25:E25"/>
     <mergeCell ref="A84:K84"/>
-    <mergeCell ref="A108:K108"/>
-    <mergeCell ref="G87:K87"/>
     <mergeCell ref="A3:K3"/>
     <mergeCell ref="G34:K34"/>
-    <mergeCell ref="A86:K86"/>
     <mergeCell ref="A2:K2"/>
     <mergeCell ref="A33:K33"/>
+    <mergeCell ref="A85:E85"/>
+    <mergeCell ref="A116:E116"/>
     <mergeCell ref="G4:K4"/>
+    <mergeCell ref="A144:E144"/>
     <mergeCell ref="A4:E4"/>
+    <mergeCell ref="G144:K144"/>
+    <mergeCell ref="G85:K85"/>
+    <mergeCell ref="G94:K94"/>
     <mergeCell ref="G25:K25"/>
+    <mergeCell ref="A115:K115"/>
+    <mergeCell ref="A93:K93"/>
   </mergeCells>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/reports/pdf_rolling5_20261023.xlsx
+++ b/reports/pdf_rolling5_20261023.xlsx
@@ -1186,23 +1186,23 @@
     <row r="18">
       <c r="A18" s="10" t="inlineStr">
         <is>
-          <t>파크시스템스</t>
+          <t>파두</t>
         </is>
       </c>
       <c r="B18" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C18" s="11" t="n">
-        <v>2958120178</v>
+        <v>586245635</v>
       </c>
       <c r="D18" s="12" t="inlineStr">
         <is>
-          <t>1.50%→2.10%</t>
+          <t>0.46%→0.52%</t>
         </is>
       </c>
       <c r="E18" s="13" t="inlineStr">
         <is>
-          <t>25→37</t>
+          <t>34→46</t>
         </is>
       </c>
       <c r="G18" s="14" t="inlineStr">
@@ -1230,23 +1230,23 @@
     <row r="19">
       <c r="A19" s="10" t="inlineStr">
         <is>
-          <t>파두</t>
+          <t>원익머트리얼즈</t>
         </is>
       </c>
       <c r="B19" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C19" s="11" t="n">
-        <v>586245635</v>
+        <v>413539225</v>
       </c>
       <c r="D19" s="12" t="inlineStr">
         <is>
-          <t>0.46%→0.52%</t>
+          <t>1.47%→1.46%</t>
         </is>
       </c>
       <c r="E19" s="13" t="inlineStr">
         <is>
-          <t>34→46</t>
+          <t>173→185</t>
         </is>
       </c>
       <c r="G19" s="17" t="n"/>
@@ -1258,23 +1258,23 @@
     <row r="20">
       <c r="A20" s="10" t="inlineStr">
         <is>
-          <t>원익머트리얼즈</t>
+          <t>파크시스템스</t>
         </is>
       </c>
       <c r="B20" s="11" t="n">
         <v>12</v>
       </c>
       <c r="C20" s="11" t="n">
-        <v>413539225</v>
+        <v>2958120178</v>
       </c>
       <c r="D20" s="12" t="inlineStr">
         <is>
-          <t>1.47%→1.46%</t>
+          <t>1.50%→2.10%</t>
         </is>
       </c>
       <c r="E20" s="13" t="inlineStr">
         <is>
-          <t>173→185</t>
+          <t>25→37</t>
         </is>
       </c>
       <c r="G20" s="17" t="n"/>
@@ -2021,23 +2021,23 @@
       </c>
       <c r="G43" s="14" t="inlineStr">
         <is>
-          <t>에스피지</t>
+          <t>비츠로셀  (편출)</t>
         </is>
       </c>
       <c r="H43" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I43" s="15" t="n">
-        <v>-2653198553</v>
+        <v>-765599582</v>
       </c>
       <c r="J43" s="16" t="inlineStr">
         <is>
-          <t>4.06%→3.16%</t>
+          <t>0.34%→0.00%</t>
         </is>
       </c>
       <c r="K43" s="13" t="inlineStr">
         <is>
-          <t>180→130</t>
+          <t>50→0</t>
         </is>
       </c>
     </row>
@@ -2109,23 +2109,23 @@
       </c>
       <c r="G45" s="14" t="inlineStr">
         <is>
-          <t>비츠로셀  (편출)</t>
+          <t>에스피지</t>
         </is>
       </c>
       <c r="H45" s="15" t="n">
         <v>-50</v>
       </c>
       <c r="I45" s="15" t="n">
-        <v>-765599582</v>
+        <v>-2653198553</v>
       </c>
       <c r="J45" s="16" t="inlineStr">
         <is>
-          <t>0.34%→0.00%</t>
+          <t>4.06%→3.16%</t>
         </is>
       </c>
       <c r="K45" s="13" t="inlineStr">
         <is>
-          <t>50→0</t>
+          <t>180→130</t>
         </is>
       </c>
     </row>
@@ -3307,7 +3307,7 @@
     <row r="84" ht="19" customHeight="1">
       <c r="A84" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,073억   ·   현금 50억(4.7%)      오늘 2026-10-23  vs  5일전 2026-10-16      매수 5종목  /  매도 3종목</t>
+          <t>■ TIGER 기술이전바이오액티브  (미래에셋)      순자산 ≈ 1,073억      오늘 2026-10-23  vs  5일전 2026-10-16      매수 5종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B84" s="4" t="n"/>
@@ -3396,23 +3396,23 @@
     <row r="87">
       <c r="A87" s="10" t="inlineStr">
         <is>
-          <t>HLB이노베이션</t>
+          <t>쓰리빌리언</t>
         </is>
       </c>
       <c r="B87" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C87" s="11" t="n">
-        <v>197992021</v>
+        <v>65706420</v>
       </c>
       <c r="D87" s="12" t="inlineStr">
         <is>
-          <t>3.10%→2.42%</t>
+          <t>1.48%→1.12%</t>
         </is>
       </c>
       <c r="E87" s="13" t="inlineStr">
         <is>
-          <t>69→75</t>
+          <t>99→105</t>
         </is>
       </c>
       <c r="G87" s="14" t="inlineStr">
@@ -3440,23 +3440,23 @@
     <row r="88">
       <c r="A88" s="10" t="inlineStr">
         <is>
-          <t>쓰리빌리언</t>
+          <t>HLB이노베이션</t>
         </is>
       </c>
       <c r="B88" s="11" t="n">
         <v>6</v>
       </c>
       <c r="C88" s="11" t="n">
-        <v>65706420</v>
+        <v>197992021</v>
       </c>
       <c r="D88" s="12" t="inlineStr">
         <is>
-          <t>1.48%→1.12%</t>
+          <t>3.10%→2.42%</t>
         </is>
       </c>
       <c r="E88" s="13" t="inlineStr">
         <is>
-          <t>99→105</t>
+          <t>69→75</t>
         </is>
       </c>
       <c r="G88" s="14" t="inlineStr">
@@ -4069,23 +4069,23 @@
     <row r="105">
       <c r="A105" s="10" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>아스플로</t>
         </is>
       </c>
       <c r="B105" s="11" t="n">
         <v>46</v>
       </c>
       <c r="C105" s="11" t="n">
-        <v>803536911</v>
+        <v>234300916</v>
       </c>
       <c r="D105" s="12" t="inlineStr">
         <is>
-          <t>1.11%→1.99%</t>
+          <t>1.95%→2.35%</t>
         </is>
       </c>
       <c r="E105" s="13" t="inlineStr">
         <is>
-          <t>50→96</t>
+          <t>343→389</t>
         </is>
       </c>
       <c r="G105" s="14" t="inlineStr">
@@ -4113,23 +4113,23 @@
     <row r="106">
       <c r="A106" s="10" t="inlineStr">
         <is>
-          <t>아스플로</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="B106" s="11" t="n">
         <v>46</v>
       </c>
       <c r="C106" s="11" t="n">
-        <v>234300916</v>
+        <v>803536911</v>
       </c>
       <c r="D106" s="12" t="inlineStr">
         <is>
-          <t>1.95%→2.35%</t>
+          <t>1.11%→1.99%</t>
         </is>
       </c>
       <c r="E106" s="13" t="inlineStr">
         <is>
-          <t>343→389</t>
+          <t>50→96</t>
         </is>
       </c>
       <c r="G106" s="14" t="inlineStr">
@@ -4401,7 +4401,7 @@
     <row r="115" ht="19" customHeight="1">
       <c r="A115" s="3" t="inlineStr">
         <is>
-          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 303억   ·   현금 7억(2.2%)      오늘 2026-10-23  vs  5일전 2026-10-16      매수 15종목  /  매도 24종목</t>
+          <t>■ TIGER 코스닥액티브  (미래에셋)      순자산 ≈ 303억      오늘 2026-10-23  vs  5일전 2026-10-16      매수 15종목  /  매도 24종목</t>
         </is>
       </c>
       <c r="B115" s="4" t="n"/>
@@ -4622,23 +4622,23 @@
     <row r="121">
       <c r="A121" s="10" t="inlineStr">
         <is>
-          <t>서진시스템</t>
+          <t>지투지바이오</t>
         </is>
       </c>
       <c r="B121" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C121" s="11" t="n">
-        <v>291291000</v>
+        <v>353496000</v>
       </c>
       <c r="D121" s="12" t="inlineStr">
         <is>
-          <t>3.63%→4.37%</t>
+          <t>0.41%→1.73%</t>
         </is>
       </c>
       <c r="E121" s="13" t="inlineStr">
         <is>
-          <t>69→89</t>
+          <t>9→29</t>
         </is>
       </c>
       <c r="G121" s="14" t="inlineStr">
@@ -4666,23 +4666,23 @@
     <row r="122">
       <c r="A122" s="10" t="inlineStr">
         <is>
-          <t>지투지바이오</t>
+          <t>서진시스템</t>
         </is>
       </c>
       <c r="B122" s="11" t="n">
         <v>20</v>
       </c>
       <c r="C122" s="11" t="n">
-        <v>353496000</v>
+        <v>291291000</v>
       </c>
       <c r="D122" s="12" t="inlineStr">
         <is>
-          <t>0.41%→1.73%</t>
+          <t>3.63%→4.37%</t>
         </is>
       </c>
       <c r="E122" s="13" t="inlineStr">
         <is>
-          <t>9→29</t>
+          <t>69→89</t>
         </is>
       </c>
       <c r="G122" s="14" t="inlineStr">
@@ -4842,23 +4842,23 @@
     <row r="126">
       <c r="A126" s="10" t="inlineStr">
         <is>
-          <t>선익시스템  (신규)</t>
+          <t>알지노믹스</t>
         </is>
       </c>
       <c r="B126" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C126" s="11" t="n">
-        <v>313513200</v>
+        <v>95366700</v>
       </c>
       <c r="D126" s="12" t="inlineStr">
         <is>
-          <t>0.00%→1.06%</t>
+          <t>0.65%→1.07%</t>
         </is>
       </c>
       <c r="E126" s="13" t="inlineStr">
         <is>
-          <t>0→9</t>
+          <t>21→30</t>
         </is>
       </c>
       <c r="G126" s="14" t="inlineStr">
@@ -4886,23 +4886,23 @@
     <row r="127">
       <c r="A127" s="10" t="inlineStr">
         <is>
-          <t>알지노믹스</t>
+          <t>선익시스템  (신규)</t>
         </is>
       </c>
       <c r="B127" s="11" t="n">
         <v>9</v>
       </c>
       <c r="C127" s="11" t="n">
-        <v>95366700</v>
+        <v>313513200</v>
       </c>
       <c r="D127" s="12" t="inlineStr">
         <is>
-          <t>0.65%→1.07%</t>
+          <t>0.00%→1.06%</t>
         </is>
       </c>
       <c r="E127" s="13" t="inlineStr">
         <is>
-          <t>21→30</t>
+          <t>0→9</t>
         </is>
       </c>
       <c r="G127" s="14" t="inlineStr">
@@ -4974,23 +4974,23 @@
     <row r="129">
       <c r="A129" s="10" t="inlineStr">
         <is>
-          <t>심텍</t>
+          <t>올릭스</t>
         </is>
       </c>
       <c r="B129" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C129" s="11" t="n">
-        <v>358858500</v>
+        <v>317116800</v>
       </c>
       <c r="D129" s="12" t="inlineStr">
         <is>
-          <t>5.01%→5.87%</t>
+          <t>2.35%→3.82%</t>
         </is>
       </c>
       <c r="E129" s="13" t="inlineStr">
         <is>
-          <t>27→34</t>
+          <t>18→25</t>
         </is>
       </c>
       <c r="G129" s="14" t="inlineStr">
@@ -5018,23 +5018,23 @@
     <row r="130">
       <c r="A130" s="10" t="inlineStr">
         <is>
-          <t>올릭스</t>
+          <t>심텍</t>
         </is>
       </c>
       <c r="B130" s="11" t="n">
         <v>7</v>
       </c>
       <c r="C130" s="11" t="n">
-        <v>317116800</v>
+        <v>358858500</v>
       </c>
       <c r="D130" s="12" t="inlineStr">
         <is>
-          <t>2.35%→3.82%</t>
+          <t>5.01%→5.87%</t>
         </is>
       </c>
       <c r="E130" s="13" t="inlineStr">
         <is>
-          <t>18→25</t>
+          <t>27→34</t>
         </is>
       </c>
       <c r="G130" s="14" t="inlineStr">
@@ -5155,23 +5155,23 @@
       <c r="E133" s="17" t="n"/>
       <c r="G133" s="14" t="inlineStr">
         <is>
-          <t>네패스</t>
+          <t>오킨스전자</t>
         </is>
       </c>
       <c r="H133" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I133" s="15" t="n">
-        <v>-110660550</v>
+        <v>-113256000</v>
       </c>
       <c r="J133" s="16" t="inlineStr">
         <is>
-          <t>1.01%→0.54%</t>
+          <t>1.26%→0.80%</t>
         </is>
       </c>
       <c r="K133" s="13" t="inlineStr">
         <is>
-          <t>27→16</t>
+          <t>34→23</t>
         </is>
       </c>
     </row>
@@ -5183,23 +5183,23 @@
       <c r="E134" s="17" t="n"/>
       <c r="G134" s="14" t="inlineStr">
         <is>
-          <t>오킨스전자</t>
+          <t>네패스</t>
         </is>
       </c>
       <c r="H134" s="15" t="n">
         <v>-11</v>
       </c>
       <c r="I134" s="15" t="n">
-        <v>-113256000</v>
+        <v>-110660550</v>
       </c>
       <c r="J134" s="16" t="inlineStr">
         <is>
-          <t>1.26%→0.80%</t>
+          <t>1.01%→0.54%</t>
         </is>
       </c>
       <c r="K134" s="13" t="inlineStr">
         <is>
-          <t>34→23</t>
+          <t>27→16</t>
         </is>
       </c>
     </row>
@@ -5323,23 +5323,23 @@
       <c r="E139" s="17" t="n"/>
       <c r="G139" s="14" t="inlineStr">
         <is>
-          <t>펌텍코리아</t>
+          <t>기가비스</t>
         </is>
       </c>
       <c r="H139" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I139" s="15" t="n">
-        <v>-119776800</v>
+        <v>-179493600</v>
       </c>
       <c r="J139" s="16" t="inlineStr">
         <is>
-          <t>3.60%→3.23%</t>
+          <t>1.16%→0.45%</t>
         </is>
       </c>
       <c r="K139" s="13" t="inlineStr">
         <is>
-          <t>36→32</t>
+          <t>7→3</t>
         </is>
       </c>
     </row>
@@ -5351,23 +5351,23 @@
       <c r="E140" s="17" t="n"/>
       <c r="G140" s="14" t="inlineStr">
         <is>
-          <t>기가비스</t>
+          <t>펌텍코리아</t>
         </is>
       </c>
       <c r="H140" s="15" t="n">
         <v>-4</v>
       </c>
       <c r="I140" s="15" t="n">
-        <v>-179493600</v>
+        <v>-119776800</v>
       </c>
       <c r="J140" s="16" t="inlineStr">
         <is>
-          <t>1.16%→0.45%</t>
+          <t>3.60%→3.23%</t>
         </is>
       </c>
       <c r="K140" s="13" t="inlineStr">
         <is>
-          <t>7→3</t>
+          <t>36→32</t>
         </is>
       </c>
     </row>
@@ -5402,7 +5402,7 @@
     <row r="143" ht="19" customHeight="1">
       <c r="A143" s="3" t="inlineStr">
         <is>
-          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 56억   ·   현금 1억(1.7%)      오늘 2026-10-23  vs  5일전 2026-10-16      매수 4종목  /  매도 3종목</t>
+          <t>■ MIDAS 코스닥액티브  (마이다스)      순자산 ≈ 56억      오늘 2026-10-23  vs  5일전 2026-10-16      매수 4종목  /  매도 3종목</t>
         </is>
       </c>
       <c r="B143" s="4" t="n"/>
